--- a/results/bonncohort/info_bonn_cohort.xlsx
+++ b/results/bonncohort/info_bonn_cohort.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D712"/>
+  <dimension ref="A1:E712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>EZ</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EZ_as_exported</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,9 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +493,9 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +514,9 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -521,6 +535,9 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -539,6 +556,9 @@
       <c r="D6" t="n">
         <v>3</v>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +577,9 @@
       <c r="D7" t="n">
         <v>2</v>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -575,6 +598,9 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -593,6 +619,9 @@
       <c r="D9" t="n">
         <v>3</v>
       </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -611,6 +640,9 @@
       <c r="D10" t="n">
         <v>2</v>
       </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -629,6 +661,9 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -647,6 +682,9 @@
       <c r="D12" t="n">
         <v>4</v>
       </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -665,6 +703,9 @@
       <c r="D13" t="n">
         <v>2</v>
       </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -683,6 +724,9 @@
       <c r="D14" t="n">
         <v>2</v>
       </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -701,6 +745,9 @@
       <c r="D15" t="n">
         <v>2</v>
       </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -719,6 +766,9 @@
       <c r="D16" t="n">
         <v>3</v>
       </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -737,6 +787,9 @@
       <c r="D17" t="n">
         <v>4</v>
       </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -755,6 +808,9 @@
       <c r="D18" t="n">
         <v>3</v>
       </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -773,6 +829,9 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -791,6 +850,9 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -809,6 +871,9 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -827,6 +892,9 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -845,6 +913,9 @@
       <c r="D23" t="n">
         <v>6</v>
       </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -863,6 +934,9 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -881,6 +955,9 @@
       <c r="D25" t="n">
         <v>5</v>
       </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -899,6 +976,9 @@
       <c r="D26" t="n">
         <v>5</v>
       </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -917,6 +997,9 @@
       <c r="D27" t="n">
         <v>4</v>
       </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -935,6 +1018,9 @@
       <c r="D28" t="n">
         <v>4</v>
       </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -953,6 +1039,9 @@
       <c r="D29" t="n">
         <v>4</v>
       </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -971,6 +1060,9 @@
       <c r="D30" t="n">
         <v>6</v>
       </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -989,6 +1081,9 @@
       <c r="D31" t="n">
         <v>2</v>
       </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1007,6 +1102,9 @@
       <c r="D32" t="n">
         <v>2</v>
       </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1025,6 +1123,9 @@
       <c r="D33" t="n">
         <v>4</v>
       </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1043,6 +1144,9 @@
       <c r="D34" t="n">
         <v>4</v>
       </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1061,6 +1165,9 @@
       <c r="D35" t="n">
         <v>4</v>
       </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1079,6 +1186,9 @@
       <c r="D36" t="n">
         <v>4</v>
       </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1097,6 +1207,9 @@
       <c r="D37" t="n">
         <v>4</v>
       </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1115,6 +1228,9 @@
       <c r="D38" t="n">
         <v>2</v>
       </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1133,6 +1249,9 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1151,6 +1270,9 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1169,6 +1291,9 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1187,6 +1312,9 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1205,6 +1333,9 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1223,6 +1354,9 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1241,6 +1375,9 @@
       <c r="D45" t="n">
         <v>2</v>
       </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1259,6 +1396,9 @@
       <c r="D46" t="n">
         <v>2</v>
       </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1277,6 +1417,9 @@
       <c r="D47" t="n">
         <v>3</v>
       </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1295,6 +1438,9 @@
       <c r="D48" t="n">
         <v>2</v>
       </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1313,6 +1459,9 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1331,6 +1480,9 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1349,6 +1501,9 @@
       <c r="D51" t="n">
         <v>2</v>
       </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1367,6 +1522,9 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1385,6 +1543,9 @@
       <c r="D53" t="n">
         <v>2</v>
       </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1403,6 +1564,9 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1421,6 +1585,9 @@
       <c r="D55" t="n">
         <v>3</v>
       </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1439,6 +1606,9 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1457,6 +1627,9 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1475,6 +1648,9 @@
       <c r="D58" t="n">
         <v>3</v>
       </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1493,6 +1669,9 @@
       <c r="D59" t="n">
         <v>3</v>
       </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1511,6 +1690,9 @@
       <c r="D60" t="n">
         <v>2</v>
       </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1529,6 +1711,9 @@
       <c r="D61" t="n">
         <v>4</v>
       </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1547,6 +1732,9 @@
       <c r="D62" t="n">
         <v>3</v>
       </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1565,6 +1753,9 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1583,6 +1774,9 @@
       <c r="D64" t="n">
         <v>2</v>
       </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1601,6 +1795,9 @@
       <c r="D65" t="n">
         <v>6</v>
       </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1619,6 +1816,9 @@
       <c r="D66" t="n">
         <v>5</v>
       </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1637,6 +1837,9 @@
       <c r="D67" t="n">
         <v>2</v>
       </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1655,6 +1858,9 @@
       <c r="D68" t="n">
         <v>2</v>
       </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1673,6 +1879,9 @@
       <c r="D69" t="n">
         <v>3</v>
       </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1691,6 +1900,9 @@
       <c r="D70" t="n">
         <v>2</v>
       </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1709,6 +1921,9 @@
       <c r="D71" t="n">
         <v>2</v>
       </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1727,6 +1942,9 @@
       <c r="D72" t="n">
         <v>2</v>
       </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1745,6 +1963,9 @@
       <c r="D73" t="n">
         <v>3</v>
       </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1763,6 +1984,9 @@
       <c r="D74" t="n">
         <v>0</v>
       </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1781,6 +2005,9 @@
       <c r="D75" t="n">
         <v>0</v>
       </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1799,6 +2026,9 @@
       <c r="D76" t="n">
         <v>0</v>
       </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1817,6 +2047,9 @@
       <c r="D77" t="n">
         <v>0</v>
       </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1835,6 +2068,9 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1853,6 +2089,9 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1871,6 +2110,9 @@
       <c r="D80" t="n">
         <v>0</v>
       </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1889,6 +2131,9 @@
       <c r="D81" t="n">
         <v>0</v>
       </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1907,6 +2152,9 @@
       <c r="D82" t="n">
         <v>2</v>
       </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1925,6 +2173,9 @@
       <c r="D83" t="n">
         <v>2</v>
       </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1943,6 +2194,9 @@
       <c r="D84" t="n">
         <v>2</v>
       </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1961,6 +2215,9 @@
       <c r="D85" t="n">
         <v>2</v>
       </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1979,6 +2236,9 @@
       <c r="D86" t="n">
         <v>2</v>
       </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1997,6 +2257,9 @@
       <c r="D87" t="n">
         <v>0</v>
       </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2015,6 +2278,9 @@
       <c r="D88" t="n">
         <v>0</v>
       </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2033,6 +2299,9 @@
       <c r="D89" t="n">
         <v>0</v>
       </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2051,6 +2320,9 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2069,6 +2341,9 @@
       <c r="D91" t="n">
         <v>2</v>
       </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2087,6 +2362,9 @@
       <c r="D92" t="n">
         <v>3</v>
       </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2105,6 +2383,9 @@
       <c r="D93" t="n">
         <v>3</v>
       </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2123,6 +2404,9 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2141,6 +2425,9 @@
       <c r="D95" t="n">
         <v>0</v>
       </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2159,6 +2446,9 @@
       <c r="D96" t="n">
         <v>0</v>
       </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2177,6 +2467,9 @@
       <c r="D97" t="n">
         <v>2</v>
       </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2195,6 +2488,9 @@
       <c r="D98" t="n">
         <v>3</v>
       </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2213,6 +2509,9 @@
       <c r="D99" t="n">
         <v>0</v>
       </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2231,6 +2530,9 @@
       <c r="D100" t="n">
         <v>1</v>
       </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2249,6 +2551,9 @@
       <c r="D101" t="n">
         <v>1</v>
       </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2267,6 +2572,9 @@
       <c r="D102" t="n">
         <v>0</v>
       </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2285,6 +2593,9 @@
       <c r="D103" t="n">
         <v>0</v>
       </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2303,6 +2614,9 @@
       <c r="D104" t="n">
         <v>0</v>
       </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2321,6 +2635,9 @@
       <c r="D105" t="n">
         <v>1</v>
       </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2339,6 +2656,9 @@
       <c r="D106" t="n">
         <v>1</v>
       </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2357,6 +2677,9 @@
       <c r="D107" t="n">
         <v>1</v>
       </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2375,6 +2698,9 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2393,6 +2719,9 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2411,6 +2740,9 @@
       <c r="D110" t="n">
         <v>0</v>
       </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2429,6 +2761,9 @@
       <c r="D111" t="n">
         <v>0</v>
       </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2447,6 +2782,9 @@
       <c r="D112" t="n">
         <v>0</v>
       </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2465,6 +2803,9 @@
       <c r="D113" t="n">
         <v>0</v>
       </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2483,6 +2824,9 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2501,6 +2845,9 @@
       <c r="D115" t="n">
         <v>0</v>
       </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2519,6 +2866,9 @@
       <c r="D116" t="n">
         <v>1</v>
       </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2537,6 +2887,9 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2555,6 +2908,9 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2573,6 +2929,9 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2591,6 +2950,9 @@
       <c r="D120" t="n">
         <v>0</v>
       </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2609,6 +2971,9 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2627,6 +2992,9 @@
       <c r="D122" t="n">
         <v>0</v>
       </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2645,6 +3013,9 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2663,6 +3034,9 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2681,6 +3055,9 @@
       <c r="D125" t="n">
         <v>0</v>
       </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2699,6 +3076,9 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2717,6 +3097,9 @@
       <c r="D127" t="n">
         <v>0</v>
       </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2735,6 +3118,9 @@
       <c r="D128" t="n">
         <v>0</v>
       </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2753,6 +3139,9 @@
       <c r="D129" t="n">
         <v>0</v>
       </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2771,6 +3160,9 @@
       <c r="D130" t="n">
         <v>1</v>
       </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2789,6 +3181,9 @@
       <c r="D131" t="n">
         <v>2</v>
       </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2807,6 +3202,9 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2825,6 +3223,9 @@
       <c r="D133" t="n">
         <v>2</v>
       </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2843,6 +3244,9 @@
       <c r="D134" t="n">
         <v>2</v>
       </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2861,6 +3265,9 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2879,6 +3286,9 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2897,6 +3307,9 @@
       <c r="D137" t="n">
         <v>2</v>
       </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2915,6 +3328,9 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2933,6 +3349,9 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2951,6 +3370,9 @@
       <c r="D140" t="n">
         <v>1</v>
       </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2969,6 +3391,9 @@
       <c r="D141" t="n">
         <v>0</v>
       </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2987,6 +3412,9 @@
       <c r="D142" t="n">
         <v>0</v>
       </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3005,6 +3433,9 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3023,6 +3454,9 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3041,6 +3475,9 @@
       <c r="D145" t="n">
         <v>0</v>
       </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3059,6 +3496,9 @@
       <c r="D146" t="n">
         <v>0</v>
       </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3077,6 +3517,9 @@
       <c r="D147" t="n">
         <v>0</v>
       </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3095,6 +3538,9 @@
       <c r="D148" t="n">
         <v>0</v>
       </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3113,6 +3559,9 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3131,6 +3580,9 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3149,6 +3601,9 @@
       <c r="D151" t="n">
         <v>0</v>
       </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3167,6 +3622,9 @@
       <c r="D152" t="n">
         <v>1</v>
       </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3185,6 +3643,9 @@
       <c r="D153" t="n">
         <v>0</v>
       </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3203,6 +3664,9 @@
       <c r="D154" t="n">
         <v>0</v>
       </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3221,6 +3685,9 @@
       <c r="D155" t="n">
         <v>0</v>
       </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3239,6 +3706,9 @@
       <c r="D156" t="n">
         <v>1</v>
       </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3257,6 +3727,9 @@
       <c r="D157" t="n">
         <v>0</v>
       </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3275,6 +3748,9 @@
       <c r="D158" t="n">
         <v>0</v>
       </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3293,6 +3769,9 @@
       <c r="D159" t="n">
         <v>0</v>
       </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3311,6 +3790,9 @@
       <c r="D160" t="n">
         <v>0</v>
       </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3329,6 +3811,9 @@
       <c r="D161" t="n">
         <v>0</v>
       </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3347,6 +3832,9 @@
       <c r="D162" t="n">
         <v>0</v>
       </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3365,6 +3853,9 @@
       <c r="D163" t="n">
         <v>0</v>
       </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3383,6 +3874,9 @@
       <c r="D164" t="n">
         <v>0</v>
       </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3401,6 +3895,9 @@
       <c r="D165" t="n">
         <v>0</v>
       </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3419,6 +3916,9 @@
       <c r="D166" t="n">
         <v>0</v>
       </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3437,6 +3937,9 @@
       <c r="D167" t="n">
         <v>0</v>
       </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3455,6 +3958,9 @@
       <c r="D168" t="n">
         <v>0</v>
       </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3473,6 +3979,9 @@
       <c r="D169" t="n">
         <v>0</v>
       </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3491,6 +4000,9 @@
       <c r="D170" t="n">
         <v>0</v>
       </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3509,6 +4021,9 @@
       <c r="D171" t="n">
         <v>0</v>
       </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3527,6 +4042,9 @@
       <c r="D172" t="n">
         <v>0</v>
       </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3545,6 +4063,9 @@
       <c r="D173" t="n">
         <v>0</v>
       </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3563,6 +4084,9 @@
       <c r="D174" t="n">
         <v>0</v>
       </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3581,6 +4105,9 @@
       <c r="D175" t="n">
         <v>0</v>
       </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3599,6 +4126,9 @@
       <c r="D176" t="n">
         <v>0</v>
       </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3617,6 +4147,9 @@
       <c r="D177" t="n">
         <v>0</v>
       </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3635,6 +4168,9 @@
       <c r="D178" t="n">
         <v>0</v>
       </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3653,6 +4189,9 @@
       <c r="D179" t="n">
         <v>0</v>
       </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3671,6 +4210,9 @@
       <c r="D180" t="n">
         <v>1</v>
       </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3689,6 +4231,9 @@
       <c r="D181" t="n">
         <v>2</v>
       </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3707,6 +4252,9 @@
       <c r="D182" t="n">
         <v>2</v>
       </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3725,6 +4273,9 @@
       <c r="D183" t="n">
         <v>2</v>
       </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3743,6 +4294,9 @@
       <c r="D184" t="n">
         <v>1</v>
       </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3761,6 +4315,9 @@
       <c r="D185" t="n">
         <v>0</v>
       </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3779,6 +4336,9 @@
       <c r="D186" t="n">
         <v>0</v>
       </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3797,6 +4357,9 @@
       <c r="D187" t="n">
         <v>0</v>
       </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3815,6 +4378,9 @@
       <c r="D188" t="n">
         <v>0</v>
       </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3833,6 +4399,9 @@
       <c r="D189" t="n">
         <v>0</v>
       </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3851,6 +4420,9 @@
       <c r="D190" t="n">
         <v>0</v>
       </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3869,6 +4441,9 @@
       <c r="D191" t="n">
         <v>0</v>
       </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3887,6 +4462,9 @@
       <c r="D192" t="n">
         <v>0</v>
       </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3905,6 +4483,9 @@
       <c r="D193" t="n">
         <v>0</v>
       </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3923,6 +4504,9 @@
       <c r="D194" t="n">
         <v>0</v>
       </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3941,6 +4525,9 @@
       <c r="D195" t="n">
         <v>0</v>
       </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3959,6 +4546,9 @@
       <c r="D196" t="n">
         <v>0</v>
       </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3977,6 +4567,9 @@
       <c r="D197" t="n">
         <v>0</v>
       </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3995,6 +4588,9 @@
       <c r="D198" t="n">
         <v>0</v>
       </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4013,6 +4609,9 @@
       <c r="D199" t="n">
         <v>0</v>
       </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4031,6 +4630,9 @@
       <c r="D200" t="n">
         <v>0</v>
       </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4049,6 +4651,9 @@
       <c r="D201" t="n">
         <v>0</v>
       </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4067,6 +4672,9 @@
       <c r="D202" t="n">
         <v>0</v>
       </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4085,6 +4693,9 @@
       <c r="D203" t="n">
         <v>0</v>
       </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4103,6 +4714,9 @@
       <c r="D204" t="n">
         <v>0</v>
       </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4121,6 +4735,9 @@
       <c r="D205" t="n">
         <v>0</v>
       </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4139,6 +4756,9 @@
       <c r="D206" t="n">
         <v>0</v>
       </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4157,6 +4777,9 @@
       <c r="D207" t="n">
         <v>0</v>
       </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4175,6 +4798,9 @@
       <c r="D208" t="n">
         <v>0</v>
       </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4193,6 +4819,9 @@
       <c r="D209" t="n">
         <v>1</v>
       </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4211,6 +4840,9 @@
       <c r="D210" t="n">
         <v>1</v>
       </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4229,6 +4861,9 @@
       <c r="D211" t="n">
         <v>0</v>
       </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4247,6 +4882,9 @@
       <c r="D212" t="n">
         <v>0</v>
       </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4265,6 +4903,9 @@
       <c r="D213" t="n">
         <v>0</v>
       </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4283,6 +4924,9 @@
       <c r="D214" t="n">
         <v>0</v>
       </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4301,6 +4945,9 @@
       <c r="D215" t="n">
         <v>0</v>
       </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4319,6 +4966,9 @@
       <c r="D216" t="n">
         <v>1</v>
       </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4337,6 +4987,9 @@
       <c r="D217" t="n">
         <v>0</v>
       </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4355,6 +5008,9 @@
       <c r="D218" t="n">
         <v>0</v>
       </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4373,6 +5029,9 @@
       <c r="D219" t="n">
         <v>0</v>
       </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4391,6 +5050,9 @@
       <c r="D220" t="n">
         <v>0</v>
       </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4409,6 +5071,9 @@
       <c r="D221" t="n">
         <v>0</v>
       </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4427,6 +5092,9 @@
       <c r="D222" t="n">
         <v>0</v>
       </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4445,6 +5113,9 @@
       <c r="D223" t="n">
         <v>1</v>
       </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4463,6 +5134,9 @@
       <c r="D224" t="n">
         <v>1</v>
       </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4481,6 +5155,9 @@
       <c r="D225" t="n">
         <v>1</v>
       </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4499,6 +5176,9 @@
       <c r="D226" t="n">
         <v>1</v>
       </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4517,6 +5197,9 @@
       <c r="D227" t="n">
         <v>1</v>
       </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4535,6 +5218,9 @@
       <c r="D228" t="n">
         <v>0</v>
       </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4553,6 +5239,9 @@
       <c r="D229" t="n">
         <v>0</v>
       </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4571,6 +5260,9 @@
       <c r="D230" t="n">
         <v>0</v>
       </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4589,6 +5281,9 @@
       <c r="D231" t="n">
         <v>0</v>
       </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4607,6 +5302,9 @@
       <c r="D232" t="n">
         <v>0</v>
       </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4625,6 +5323,9 @@
       <c r="D233" t="n">
         <v>0</v>
       </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4643,6 +5344,9 @@
       <c r="D234" t="n">
         <v>0</v>
       </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4661,6 +5365,9 @@
       <c r="D235" t="n">
         <v>0</v>
       </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4679,6 +5386,9 @@
       <c r="D236" t="n">
         <v>1</v>
       </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4697,6 +5407,9 @@
       <c r="D237" t="n">
         <v>0</v>
       </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4715,6 +5428,9 @@
       <c r="D238" t="n">
         <v>1</v>
       </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4733,6 +5449,9 @@
       <c r="D239" t="n">
         <v>0</v>
       </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4751,6 +5470,9 @@
       <c r="D240" t="n">
         <v>1</v>
       </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4769,6 +5491,9 @@
       <c r="D241" t="n">
         <v>1</v>
       </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4787,6 +5512,9 @@
       <c r="D242" t="n">
         <v>1</v>
       </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4805,6 +5533,9 @@
       <c r="D243" t="n">
         <v>2</v>
       </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4823,6 +5554,9 @@
       <c r="D244" t="n">
         <v>0</v>
       </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4841,6 +5575,9 @@
       <c r="D245" t="n">
         <v>1</v>
       </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4859,6 +5596,9 @@
       <c r="D246" t="n">
         <v>1</v>
       </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4877,6 +5617,9 @@
       <c r="D247" t="n">
         <v>1</v>
       </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4895,6 +5638,9 @@
       <c r="D248" t="n">
         <v>0</v>
       </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4913,6 +5659,9 @@
       <c r="D249" t="n">
         <v>0</v>
       </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4931,6 +5680,9 @@
       <c r="D250" t="n">
         <v>0</v>
       </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4949,6 +5701,9 @@
       <c r="D251" t="n">
         <v>0</v>
       </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4967,6 +5722,9 @@
       <c r="D252" t="n">
         <v>0</v>
       </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4985,6 +5743,9 @@
       <c r="D253" t="n">
         <v>0</v>
       </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5003,6 +5764,9 @@
       <c r="D254" t="n">
         <v>0</v>
       </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5021,6 +5785,9 @@
       <c r="D255" t="n">
         <v>0</v>
       </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5039,6 +5806,9 @@
       <c r="D256" t="n">
         <v>0</v>
       </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5057,6 +5827,9 @@
       <c r="D257" t="n">
         <v>0</v>
       </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5075,6 +5848,9 @@
       <c r="D258" t="n">
         <v>1</v>
       </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5093,6 +5869,9 @@
       <c r="D259" t="n">
         <v>1</v>
       </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5111,6 +5890,9 @@
       <c r="D260" t="n">
         <v>1</v>
       </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5129,6 +5911,9 @@
       <c r="D261" t="n">
         <v>0</v>
       </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5147,6 +5932,9 @@
       <c r="D262" t="n">
         <v>0</v>
       </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5165,6 +5953,9 @@
       <c r="D263" t="n">
         <v>0</v>
       </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5183,6 +5974,9 @@
       <c r="D264" t="n">
         <v>0</v>
       </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5201,6 +5995,9 @@
       <c r="D265" t="n">
         <v>0</v>
       </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5219,6 +6016,9 @@
       <c r="D266" t="n">
         <v>0</v>
       </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5237,6 +6037,9 @@
       <c r="D267" t="n">
         <v>0</v>
       </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5255,6 +6058,9 @@
       <c r="D268" t="n">
         <v>0</v>
       </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5273,6 +6079,9 @@
       <c r="D269" t="n">
         <v>0</v>
       </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5291,6 +6100,9 @@
       <c r="D270" t="n">
         <v>1</v>
       </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5309,6 +6121,9 @@
       <c r="D271" t="n">
         <v>1</v>
       </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5327,6 +6142,9 @@
       <c r="D272" t="n">
         <v>0</v>
       </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5345,6 +6163,9 @@
       <c r="D273" t="n">
         <v>0</v>
       </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5363,6 +6184,9 @@
       <c r="D274" t="n">
         <v>0</v>
       </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5381,6 +6205,9 @@
       <c r="D275" t="n">
         <v>0</v>
       </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5399,6 +6226,9 @@
       <c r="D276" t="n">
         <v>0</v>
       </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5417,6 +6247,9 @@
       <c r="D277" t="n">
         <v>1</v>
       </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5435,6 +6268,9 @@
       <c r="D278" t="n">
         <v>0</v>
       </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5453,6 +6289,9 @@
       <c r="D279" t="n">
         <v>0</v>
       </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5471,6 +6310,9 @@
       <c r="D280" t="n">
         <v>0</v>
       </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5489,6 +6331,9 @@
       <c r="D281" t="n">
         <v>0</v>
       </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5507,6 +6352,9 @@
       <c r="D282" t="n">
         <v>0</v>
       </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5525,6 +6373,9 @@
       <c r="D283" t="n">
         <v>0</v>
       </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5543,6 +6394,9 @@
       <c r="D284" t="n">
         <v>0</v>
       </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5561,6 +6415,9 @@
       <c r="D285" t="n">
         <v>0</v>
       </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5579,6 +6436,9 @@
       <c r="D286" t="n">
         <v>1</v>
       </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5597,6 +6457,9 @@
       <c r="D287" t="n">
         <v>0</v>
       </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5615,6 +6478,9 @@
       <c r="D288" t="n">
         <v>1</v>
       </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5633,6 +6499,9 @@
       <c r="D289" t="n">
         <v>0</v>
       </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5651,6 +6520,9 @@
       <c r="D290" t="n">
         <v>1</v>
       </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5669,6 +6541,9 @@
       <c r="D291" t="n">
         <v>1</v>
       </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5687,6 +6562,9 @@
       <c r="D292" t="n">
         <v>0</v>
       </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5705,6 +6583,9 @@
       <c r="D293" t="n">
         <v>0</v>
       </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5723,6 +6604,9 @@
       <c r="D294" t="n">
         <v>0</v>
       </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5741,6 +6625,9 @@
       <c r="D295" t="n">
         <v>0</v>
       </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5759,6 +6646,9 @@
       <c r="D296" t="n">
         <v>0</v>
       </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5777,6 +6667,9 @@
       <c r="D297" t="n">
         <v>0</v>
       </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5795,6 +6688,9 @@
       <c r="D298" t="n">
         <v>0</v>
       </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5813,6 +6709,9 @@
       <c r="D299" t="n">
         <v>1</v>
       </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5831,6 +6730,9 @@
       <c r="D300" t="n">
         <v>0</v>
       </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5849,6 +6751,9 @@
       <c r="D301" t="n">
         <v>0</v>
       </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5867,6 +6772,9 @@
       <c r="D302" t="n">
         <v>0</v>
       </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5885,6 +6793,9 @@
       <c r="D303" t="n">
         <v>0</v>
       </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5903,6 +6814,9 @@
       <c r="D304" t="n">
         <v>0</v>
       </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5921,6 +6835,9 @@
       <c r="D305" t="n">
         <v>0</v>
       </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5939,6 +6856,9 @@
       <c r="D306" t="n">
         <v>0</v>
       </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5957,6 +6877,9 @@
       <c r="D307" t="n">
         <v>1</v>
       </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5975,6 +6898,9 @@
       <c r="D308" t="n">
         <v>2</v>
       </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5993,6 +6919,9 @@
       <c r="D309" t="n">
         <v>2</v>
       </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6011,6 +6940,9 @@
       <c r="D310" t="n">
         <v>3</v>
       </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6029,6 +6961,9 @@
       <c r="D311" t="n">
         <v>3</v>
       </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6047,6 +6982,9 @@
       <c r="D312" t="n">
         <v>2</v>
       </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6065,6 +7003,9 @@
       <c r="D313" t="n">
         <v>2</v>
       </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6083,6 +7024,9 @@
       <c r="D314" t="n">
         <v>3</v>
       </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6101,6 +7045,9 @@
       <c r="D315" t="n">
         <v>2</v>
       </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6119,6 +7066,9 @@
       <c r="D316" t="n">
         <v>1</v>
       </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6137,6 +7087,9 @@
       <c r="D317" t="n">
         <v>3</v>
       </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6155,6 +7108,9 @@
       <c r="D318" t="n">
         <v>2</v>
       </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6173,6 +7129,9 @@
       <c r="D319" t="n">
         <v>2</v>
       </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6191,6 +7150,9 @@
       <c r="D320" t="n">
         <v>2</v>
       </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6209,6 +7171,9 @@
       <c r="D321" t="n">
         <v>2</v>
       </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6227,6 +7192,9 @@
       <c r="D322" t="n">
         <v>2</v>
       </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6245,6 +7213,9 @@
       <c r="D323" t="n">
         <v>2</v>
       </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6263,6 +7234,9 @@
       <c r="D324" t="n">
         <v>2</v>
       </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6281,6 +7255,9 @@
       <c r="D325" t="n">
         <v>2</v>
       </c>
+      <c r="E325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6299,6 +7276,9 @@
       <c r="D326" t="n">
         <v>1</v>
       </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6317,6 +7297,9 @@
       <c r="D327" t="n">
         <v>3</v>
       </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6335,6 +7318,9 @@
       <c r="D328" t="n">
         <v>4</v>
       </c>
+      <c r="E328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6353,6 +7339,9 @@
       <c r="D329" t="n">
         <v>3</v>
       </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6371,6 +7360,9 @@
       <c r="D330" t="n">
         <v>3</v>
       </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6389,6 +7381,9 @@
       <c r="D331" t="n">
         <v>2</v>
       </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -6407,6 +7402,9 @@
       <c r="D332" t="n">
         <v>1</v>
       </c>
+      <c r="E332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6425,6 +7423,9 @@
       <c r="D333" t="n">
         <v>0</v>
       </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6443,6 +7444,9 @@
       <c r="D334" t="n">
         <v>1</v>
       </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6461,6 +7465,9 @@
       <c r="D335" t="n">
         <v>4</v>
       </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6479,6 +7486,9 @@
       <c r="D336" t="n">
         <v>4</v>
       </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6497,6 +7507,9 @@
       <c r="D337" t="n">
         <v>3</v>
       </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6515,6 +7528,9 @@
       <c r="D338" t="n">
         <v>2</v>
       </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6533,6 +7549,9 @@
       <c r="D339" t="n">
         <v>0</v>
       </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6551,6 +7570,9 @@
       <c r="D340" t="n">
         <v>0</v>
       </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6569,6 +7591,9 @@
       <c r="D341" t="n">
         <v>0</v>
       </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6587,6 +7612,9 @@
       <c r="D342" t="n">
         <v>0</v>
       </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6605,6 +7633,9 @@
       <c r="D343" t="n">
         <v>0</v>
       </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6623,6 +7654,9 @@
       <c r="D344" t="n">
         <v>0</v>
       </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6641,6 +7675,9 @@
       <c r="D345" t="n">
         <v>0</v>
       </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6659,6 +7696,9 @@
       <c r="D346" t="n">
         <v>0</v>
       </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6677,6 +7717,9 @@
       <c r="D347" t="n">
         <v>0</v>
       </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6695,6 +7738,9 @@
       <c r="D348" t="n">
         <v>0</v>
       </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6713,6 +7759,9 @@
       <c r="D349" t="n">
         <v>0</v>
       </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6731,6 +7780,9 @@
       <c r="D350" t="n">
         <v>0</v>
       </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6749,6 +7801,9 @@
       <c r="D351" t="n">
         <v>0</v>
       </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6767,6 +7822,9 @@
       <c r="D352" t="n">
         <v>0</v>
       </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6785,6 +7843,9 @@
       <c r="D353" t="n">
         <v>0</v>
       </c>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6803,6 +7864,9 @@
       <c r="D354" t="n">
         <v>2</v>
       </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6821,6 +7885,9 @@
       <c r="D355" t="n">
         <v>0</v>
       </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6839,6 +7906,9 @@
       <c r="D356" t="n">
         <v>0</v>
       </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6857,6 +7927,9 @@
       <c r="D357" t="n">
         <v>1</v>
       </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6875,6 +7948,9 @@
       <c r="D358" t="n">
         <v>1</v>
       </c>
+      <c r="E358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6893,6 +7969,9 @@
       <c r="D359" t="n">
         <v>1</v>
       </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6911,6 +7990,9 @@
       <c r="D360" t="n">
         <v>2</v>
       </c>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6929,6 +8011,9 @@
       <c r="D361" t="n">
         <v>3</v>
       </c>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6947,6 +8032,9 @@
       <c r="D362" t="n">
         <v>2</v>
       </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6965,6 +8053,9 @@
       <c r="D363" t="n">
         <v>2</v>
       </c>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6983,6 +8074,9 @@
       <c r="D364" t="n">
         <v>2</v>
       </c>
+      <c r="E364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -7001,6 +8095,9 @@
       <c r="D365" t="n">
         <v>2</v>
       </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -7019,6 +8116,9 @@
       <c r="D366" t="n">
         <v>1</v>
       </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -7037,6 +8137,9 @@
       <c r="D367" t="n">
         <v>0</v>
       </c>
+      <c r="E367" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -7055,6 +8158,9 @@
       <c r="D368" t="n">
         <v>3</v>
       </c>
+      <c r="E368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -7073,6 +8179,9 @@
       <c r="D369" t="n">
         <v>4</v>
       </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -7091,6 +8200,9 @@
       <c r="D370" t="n">
         <v>2</v>
       </c>
+      <c r="E370" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -7109,6 +8221,9 @@
       <c r="D371" t="n">
         <v>1</v>
       </c>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -7127,6 +8242,9 @@
       <c r="D372" t="n">
         <v>3</v>
       </c>
+      <c r="E372" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -7145,6 +8263,9 @@
       <c r="D373" t="n">
         <v>2</v>
       </c>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -7163,6 +8284,9 @@
       <c r="D374" t="n">
         <v>3</v>
       </c>
+      <c r="E374" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -7181,6 +8305,9 @@
       <c r="D375" t="n">
         <v>1</v>
       </c>
+      <c r="E375" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -7199,6 +8326,9 @@
       <c r="D376" t="n">
         <v>2</v>
       </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -7217,6 +8347,9 @@
       <c r="D377" t="n">
         <v>2</v>
       </c>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -7235,6 +8368,9 @@
       <c r="D378" t="n">
         <v>0</v>
       </c>
+      <c r="E378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -7253,6 +8389,9 @@
       <c r="D379" t="n">
         <v>1</v>
       </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -7271,6 +8410,9 @@
       <c r="D380" t="n">
         <v>2</v>
       </c>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -7289,6 +8431,9 @@
       <c r="D381" t="n">
         <v>3</v>
       </c>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -7307,6 +8452,9 @@
       <c r="D382" t="n">
         <v>1</v>
       </c>
+      <c r="E382" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -7325,6 +8473,9 @@
       <c r="D383" t="n">
         <v>3</v>
       </c>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -7343,6 +8494,9 @@
       <c r="D384" t="n">
         <v>2</v>
       </c>
+      <c r="E384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -7361,6 +8515,9 @@
       <c r="D385" t="n">
         <v>3</v>
       </c>
+      <c r="E385" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -7379,6 +8536,9 @@
       <c r="D386" t="n">
         <v>0</v>
       </c>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -7397,6 +8557,9 @@
       <c r="D387" t="n">
         <v>0</v>
       </c>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -7415,6 +8578,9 @@
       <c r="D388" t="n">
         <v>1</v>
       </c>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -7433,6 +8599,9 @@
       <c r="D389" t="n">
         <v>2</v>
       </c>
+      <c r="E389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -7451,6 +8620,9 @@
       <c r="D390" t="n">
         <v>2</v>
       </c>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -7469,6 +8641,9 @@
       <c r="D391" t="n">
         <v>0</v>
       </c>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7487,6 +8662,9 @@
       <c r="D392" t="n">
         <v>1</v>
       </c>
+      <c r="E392" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -7505,6 +8683,9 @@
       <c r="D393" t="n">
         <v>2</v>
       </c>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -7523,6 +8704,9 @@
       <c r="D394" t="n">
         <v>3</v>
       </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -7541,6 +8725,9 @@
       <c r="D395" t="n">
         <v>3</v>
       </c>
+      <c r="E395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -7559,6 +8746,9 @@
       <c r="D396" t="n">
         <v>1</v>
       </c>
+      <c r="E396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -7577,6 +8767,9 @@
       <c r="D397" t="n">
         <v>1</v>
       </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -7595,6 +8788,9 @@
       <c r="D398" t="n">
         <v>1</v>
       </c>
+      <c r="E398" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -7613,6 +8809,9 @@
       <c r="D399" t="n">
         <v>0</v>
       </c>
+      <c r="E399" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -7631,6 +8830,9 @@
       <c r="D400" t="n">
         <v>2</v>
       </c>
+      <c r="E400" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -7649,6 +8851,9 @@
       <c r="D401" t="n">
         <v>1</v>
       </c>
+      <c r="E401" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -7667,6 +8872,9 @@
       <c r="D402" t="n">
         <v>0</v>
       </c>
+      <c r="E402" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -7685,6 +8893,9 @@
       <c r="D403" t="n">
         <v>0</v>
       </c>
+      <c r="E403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -7703,6 +8914,9 @@
       <c r="D404" t="n">
         <v>0</v>
       </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -7721,6 +8935,9 @@
       <c r="D405" t="n">
         <v>0</v>
       </c>
+      <c r="E405" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -7739,6 +8956,9 @@
       <c r="D406" t="n">
         <v>0</v>
       </c>
+      <c r="E406" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -7757,6 +8977,9 @@
       <c r="D407" t="n">
         <v>2</v>
       </c>
+      <c r="E407" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -7775,6 +8998,9 @@
       <c r="D408" t="n">
         <v>2</v>
       </c>
+      <c r="E408" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -7793,6 +9019,9 @@
       <c r="D409" t="n">
         <v>2</v>
       </c>
+      <c r="E409" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -7811,6 +9040,9 @@
       <c r="D410" t="n">
         <v>1</v>
       </c>
+      <c r="E410" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7829,6 +9061,9 @@
       <c r="D411" t="n">
         <v>0</v>
       </c>
+      <c r="E411" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7847,6 +9082,9 @@
       <c r="D412" t="n">
         <v>0</v>
       </c>
+      <c r="E412" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7865,6 +9103,9 @@
       <c r="D413" t="n">
         <v>0</v>
       </c>
+      <c r="E413" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7883,6 +9124,9 @@
       <c r="D414" t="n">
         <v>0</v>
       </c>
+      <c r="E414" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -7901,6 +9145,9 @@
       <c r="D415" t="n">
         <v>0</v>
       </c>
+      <c r="E415" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -7919,6 +9166,9 @@
       <c r="D416" t="n">
         <v>1</v>
       </c>
+      <c r="E416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -7937,6 +9187,9 @@
       <c r="D417" t="n">
         <v>0</v>
       </c>
+      <c r="E417" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -7955,6 +9208,9 @@
       <c r="D418" t="n">
         <v>0</v>
       </c>
+      <c r="E418" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -7973,6 +9229,9 @@
       <c r="D419" t="n">
         <v>2</v>
       </c>
+      <c r="E419" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -7991,6 +9250,9 @@
       <c r="D420" t="n">
         <v>1</v>
       </c>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -8009,6 +9271,9 @@
       <c r="D421" t="n">
         <v>2</v>
       </c>
+      <c r="E421" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8027,6 +9292,9 @@
       <c r="D422" t="n">
         <v>1</v>
       </c>
+      <c r="E422" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -8045,6 +9313,9 @@
       <c r="D423" t="n">
         <v>2</v>
       </c>
+      <c r="E423" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8063,6 +9334,9 @@
       <c r="D424" t="n">
         <v>2</v>
       </c>
+      <c r="E424" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8081,6 +9355,9 @@
       <c r="D425" t="n">
         <v>2</v>
       </c>
+      <c r="E425" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8099,6 +9376,9 @@
       <c r="D426" t="n">
         <v>3</v>
       </c>
+      <c r="E426" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8117,6 +9397,9 @@
       <c r="D427" t="n">
         <v>3</v>
       </c>
+      <c r="E427" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8135,6 +9418,9 @@
       <c r="D428" t="n">
         <v>2</v>
       </c>
+      <c r="E428" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8153,6 +9439,9 @@
       <c r="D429" t="n">
         <v>2</v>
       </c>
+      <c r="E429" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -8171,6 +9460,9 @@
       <c r="D430" t="n">
         <v>3</v>
       </c>
+      <c r="E430" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -8189,6 +9481,9 @@
       <c r="D431" t="n">
         <v>3</v>
       </c>
+      <c r="E431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -8207,6 +9502,9 @@
       <c r="D432" t="n">
         <v>1</v>
       </c>
+      <c r="E432" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -8225,6 +9523,9 @@
       <c r="D433" t="n">
         <v>2</v>
       </c>
+      <c r="E433" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -8243,6 +9544,9 @@
       <c r="D434" t="n">
         <v>1</v>
       </c>
+      <c r="E434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -8261,6 +9565,9 @@
       <c r="D435" t="n">
         <v>0</v>
       </c>
+      <c r="E435" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -8279,6 +9586,9 @@
       <c r="D436" t="n">
         <v>2</v>
       </c>
+      <c r="E436" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -8297,6 +9607,9 @@
       <c r="D437" t="n">
         <v>1</v>
       </c>
+      <c r="E437" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -8315,6 +9628,9 @@
       <c r="D438" t="n">
         <v>1</v>
       </c>
+      <c r="E438" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -8333,6 +9649,9 @@
       <c r="D439" t="n">
         <v>1</v>
       </c>
+      <c r="E439" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -8351,6 +9670,9 @@
       <c r="D440" t="n">
         <v>1</v>
       </c>
+      <c r="E440" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -8369,6 +9691,9 @@
       <c r="D441" t="n">
         <v>1</v>
       </c>
+      <c r="E441" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -8387,6 +9712,9 @@
       <c r="D442" t="n">
         <v>1</v>
       </c>
+      <c r="E442" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -8405,6 +9733,9 @@
       <c r="D443" t="n">
         <v>1</v>
       </c>
+      <c r="E443" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -8423,6 +9754,9 @@
       <c r="D444" t="n">
         <v>0</v>
       </c>
+      <c r="E444" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -8441,6 +9775,9 @@
       <c r="D445" t="n">
         <v>1</v>
       </c>
+      <c r="E445" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -8459,6 +9796,9 @@
       <c r="D446" t="n">
         <v>1</v>
       </c>
+      <c r="E446" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -8477,6 +9817,9 @@
       <c r="D447" t="n">
         <v>0</v>
       </c>
+      <c r="E447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -8495,6 +9838,9 @@
       <c r="D448" t="n">
         <v>0</v>
       </c>
+      <c r="E448" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -8513,6 +9859,9 @@
       <c r="D449" t="n">
         <v>0</v>
       </c>
+      <c r="E449" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8531,6 +9880,9 @@
       <c r="D450" t="n">
         <v>0</v>
       </c>
+      <c r="E450" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8549,6 +9901,9 @@
       <c r="D451" t="n">
         <v>1</v>
       </c>
+      <c r="E451" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -8567,6 +9922,9 @@
       <c r="D452" t="n">
         <v>0</v>
       </c>
+      <c r="E452" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -8585,6 +9943,9 @@
       <c r="D453" t="n">
         <v>2</v>
       </c>
+      <c r="E453" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -8603,6 +9964,9 @@
       <c r="D454" t="n">
         <v>1</v>
       </c>
+      <c r="E454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -8621,6 +9985,9 @@
       <c r="D455" t="n">
         <v>2</v>
       </c>
+      <c r="E455" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -8639,6 +10006,9 @@
       <c r="D456" t="n">
         <v>2</v>
       </c>
+      <c r="E456" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -8657,6 +10027,9 @@
       <c r="D457" t="n">
         <v>2</v>
       </c>
+      <c r="E457" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -8675,6 +10048,9 @@
       <c r="D458" t="n">
         <v>1</v>
       </c>
+      <c r="E458" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -8693,6 +10069,9 @@
       <c r="D459" t="n">
         <v>3</v>
       </c>
+      <c r="E459" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -8711,6 +10090,9 @@
       <c r="D460" t="n">
         <v>5</v>
       </c>
+      <c r="E460" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -8729,6 +10111,9 @@
       <c r="D461" t="n">
         <v>2</v>
       </c>
+      <c r="E461" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -8747,6 +10132,9 @@
       <c r="D462" t="n">
         <v>3</v>
       </c>
+      <c r="E462" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -8765,6 +10153,9 @@
       <c r="D463" t="n">
         <v>2</v>
       </c>
+      <c r="E463" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -8783,6 +10174,9 @@
       <c r="D464" t="n">
         <v>3</v>
       </c>
+      <c r="E464" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -8801,6 +10195,9 @@
       <c r="D465" t="n">
         <v>3</v>
       </c>
+      <c r="E465" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -8819,6 +10216,9 @@
       <c r="D466" t="n">
         <v>2</v>
       </c>
+      <c r="E466" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -8837,6 +10237,9 @@
       <c r="D467" t="n">
         <v>4</v>
       </c>
+      <c r="E467" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -8855,6 +10258,9 @@
       <c r="D468" t="n">
         <v>3</v>
       </c>
+      <c r="E468" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -8873,6 +10279,9 @@
       <c r="D469" t="n">
         <v>3</v>
       </c>
+      <c r="E469" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -8891,6 +10300,9 @@
       <c r="D470" t="n">
         <v>2</v>
       </c>
+      <c r="E470" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -8909,6 +10321,9 @@
       <c r="D471" t="n">
         <v>2</v>
       </c>
+      <c r="E471" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -8927,6 +10342,9 @@
       <c r="D472" t="n">
         <v>1</v>
       </c>
+      <c r="E472" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -8945,6 +10363,9 @@
       <c r="D473" t="n">
         <v>2</v>
       </c>
+      <c r="E473" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -8963,6 +10384,9 @@
       <c r="D474" t="n">
         <v>1</v>
       </c>
+      <c r="E474" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -8981,6 +10405,9 @@
       <c r="D475" t="n">
         <v>1</v>
       </c>
+      <c r="E475" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -8999,6 +10426,9 @@
       <c r="D476" t="n">
         <v>2</v>
       </c>
+      <c r="E476" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -9017,6 +10447,9 @@
       <c r="D477" t="n">
         <v>1</v>
       </c>
+      <c r="E477" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -9035,6 +10468,9 @@
       <c r="D478" t="n">
         <v>1</v>
       </c>
+      <c r="E478" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9053,6 +10489,9 @@
       <c r="D479" t="n">
         <v>1</v>
       </c>
+      <c r="E479" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -9071,6 +10510,9 @@
       <c r="D480" t="n">
         <v>1</v>
       </c>
+      <c r="E480" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -9089,6 +10531,9 @@
       <c r="D481" t="n">
         <v>1</v>
       </c>
+      <c r="E481" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -9107,6 +10552,9 @@
       <c r="D482" t="n">
         <v>1</v>
       </c>
+      <c r="E482" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -9125,6 +10573,9 @@
       <c r="D483" t="n">
         <v>1</v>
       </c>
+      <c r="E483" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -9143,6 +10594,9 @@
       <c r="D484" t="n">
         <v>0</v>
       </c>
+      <c r="E484" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -9161,6 +10615,9 @@
       <c r="D485" t="n">
         <v>1</v>
       </c>
+      <c r="E485" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -9179,6 +10636,9 @@
       <c r="D486" t="n">
         <v>1</v>
       </c>
+      <c r="E486" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -9197,6 +10657,9 @@
       <c r="D487" t="n">
         <v>3</v>
       </c>
+      <c r="E487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -9215,6 +10678,9 @@
       <c r="D488" t="n">
         <v>3</v>
       </c>
+      <c r="E488" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -9233,6 +10699,9 @@
       <c r="D489" t="n">
         <v>2</v>
       </c>
+      <c r="E489" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -9251,6 +10720,9 @@
       <c r="D490" t="n">
         <v>2</v>
       </c>
+      <c r="E490" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -9269,6 +10741,9 @@
       <c r="D491" t="n">
         <v>3</v>
       </c>
+      <c r="E491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -9287,6 +10762,9 @@
       <c r="D492" t="n">
         <v>3</v>
       </c>
+      <c r="E492" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -9305,6 +10783,9 @@
       <c r="D493" t="n">
         <v>2</v>
       </c>
+      <c r="E493" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -9323,6 +10804,9 @@
       <c r="D494" t="n">
         <v>3</v>
       </c>
+      <c r="E494" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -9341,6 +10825,9 @@
       <c r="D495" t="n">
         <v>4</v>
       </c>
+      <c r="E495" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -9359,6 +10846,9 @@
       <c r="D496" t="n">
         <v>2</v>
       </c>
+      <c r="E496" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -9377,6 +10867,9 @@
       <c r="D497" t="n">
         <v>2</v>
       </c>
+      <c r="E497" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -9395,6 +10888,9 @@
       <c r="D498" t="n">
         <v>3</v>
       </c>
+      <c r="E498" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -9413,6 +10909,9 @@
       <c r="D499" t="n">
         <v>4</v>
       </c>
+      <c r="E499" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -9431,6 +10930,9 @@
       <c r="D500" t="n">
         <v>3</v>
       </c>
+      <c r="E500" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -9449,6 +10951,9 @@
       <c r="D501" t="n">
         <v>4</v>
       </c>
+      <c r="E501" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -9467,6 +10972,9 @@
       <c r="D502" t="n">
         <v>6</v>
       </c>
+      <c r="E502" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -9485,6 +10993,9 @@
       <c r="D503" t="n">
         <v>7</v>
       </c>
+      <c r="E503" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -9503,6 +11014,9 @@
       <c r="D504" t="n">
         <v>2</v>
       </c>
+      <c r="E504" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -9521,6 +11035,9 @@
       <c r="D505" t="n">
         <v>1</v>
       </c>
+      <c r="E505" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -9539,6 +11056,9 @@
       <c r="D506" t="n">
         <v>0</v>
       </c>
+      <c r="E506" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -9557,6 +11077,9 @@
       <c r="D507" t="n">
         <v>0</v>
       </c>
+      <c r="E507" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -9575,6 +11098,9 @@
       <c r="D508" t="n">
         <v>0</v>
       </c>
+      <c r="E508" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -9593,6 +11119,9 @@
       <c r="D509" t="n">
         <v>1</v>
       </c>
+      <c r="E509" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -9611,6 +11140,9 @@
       <c r="D510" t="n">
         <v>2</v>
       </c>
+      <c r="E510" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -9629,6 +11161,9 @@
       <c r="D511" t="n">
         <v>2</v>
       </c>
+      <c r="E511" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -9647,6 +11182,9 @@
       <c r="D512" t="n">
         <v>0</v>
       </c>
+      <c r="E512" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -9665,6 +11203,9 @@
       <c r="D513" t="n">
         <v>0</v>
       </c>
+      <c r="E513" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -9683,6 +11224,9 @@
       <c r="D514" t="n">
         <v>0</v>
       </c>
+      <c r="E514" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -9701,6 +11245,9 @@
       <c r="D515" t="n">
         <v>1</v>
       </c>
+      <c r="E515" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -9719,6 +11266,9 @@
       <c r="D516" t="n">
         <v>0</v>
       </c>
+      <c r="E516" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -9737,6 +11287,9 @@
       <c r="D517" t="n">
         <v>0</v>
       </c>
+      <c r="E517" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -9755,6 +11308,9 @@
       <c r="D518" t="n">
         <v>3</v>
       </c>
+      <c r="E518" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -9773,6 +11329,9 @@
       <c r="D519" t="n">
         <v>1</v>
       </c>
+      <c r="E519" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -9791,6 +11350,9 @@
       <c r="D520" t="n">
         <v>3</v>
       </c>
+      <c r="E520" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -9809,6 +11371,9 @@
       <c r="D521" t="n">
         <v>2</v>
       </c>
+      <c r="E521" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -9827,6 +11392,9 @@
       <c r="D522" t="n">
         <v>2</v>
       </c>
+      <c r="E522" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -9845,6 +11413,9 @@
       <c r="D523" t="n">
         <v>3</v>
       </c>
+      <c r="E523" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -9863,6 +11434,9 @@
       <c r="D524" t="n">
         <v>2</v>
       </c>
+      <c r="E524" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -9881,6 +11455,9 @@
       <c r="D525" t="n">
         <v>3</v>
       </c>
+      <c r="E525" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -9899,6 +11476,9 @@
       <c r="D526" t="n">
         <v>3</v>
       </c>
+      <c r="E526" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -9917,6 +11497,9 @@
       <c r="D527" t="n">
         <v>3</v>
       </c>
+      <c r="E527" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -9935,6 +11518,9 @@
       <c r="D528" t="n">
         <v>3</v>
       </c>
+      <c r="E528" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -9953,6 +11539,9 @@
       <c r="D529" t="n">
         <v>3</v>
       </c>
+      <c r="E529" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -9971,6 +11560,9 @@
       <c r="D530" t="n">
         <v>3</v>
       </c>
+      <c r="E530" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -9989,6 +11581,9 @@
       <c r="D531" t="n">
         <v>3</v>
       </c>
+      <c r="E531" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -10007,6 +11602,9 @@
       <c r="D532" t="n">
         <v>2</v>
       </c>
+      <c r="E532" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -10025,6 +11623,9 @@
       <c r="D533" t="n">
         <v>2</v>
       </c>
+      <c r="E533" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -10043,6 +11644,9 @@
       <c r="D534" t="n">
         <v>2</v>
       </c>
+      <c r="E534" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -10061,6 +11665,9 @@
       <c r="D535" t="n">
         <v>3</v>
       </c>
+      <c r="E535" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -10079,6 +11686,9 @@
       <c r="D536" t="n">
         <v>2</v>
       </c>
+      <c r="E536" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -10097,6 +11707,9 @@
       <c r="D537" t="n">
         <v>2</v>
       </c>
+      <c r="E537" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -10115,6 +11728,9 @@
       <c r="D538" t="n">
         <v>2</v>
       </c>
+      <c r="E538" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -10133,6 +11749,9 @@
       <c r="D539" t="n">
         <v>0</v>
       </c>
+      <c r="E539" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -10151,6 +11770,9 @@
       <c r="D540" t="n">
         <v>2</v>
       </c>
+      <c r="E540" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -10169,6 +11791,9 @@
       <c r="D541" t="n">
         <v>1</v>
       </c>
+      <c r="E541" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -10187,6 +11812,9 @@
       <c r="D542" t="n">
         <v>1</v>
       </c>
+      <c r="E542" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -10205,6 +11833,9 @@
       <c r="D543" t="n">
         <v>1</v>
       </c>
+      <c r="E543" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -10223,6 +11854,9 @@
       <c r="D544" t="n">
         <v>1</v>
       </c>
+      <c r="E544" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -10241,6 +11875,9 @@
       <c r="D545" t="n">
         <v>1</v>
       </c>
+      <c r="E545" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -10259,6 +11896,9 @@
       <c r="D546" t="n">
         <v>1</v>
       </c>
+      <c r="E546" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -10277,6 +11917,9 @@
       <c r="D547" t="n">
         <v>2</v>
       </c>
+      <c r="E547" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -10295,6 +11938,9 @@
       <c r="D548" t="n">
         <v>2</v>
       </c>
+      <c r="E548" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -10313,6 +11959,9 @@
       <c r="D549" t="n">
         <v>3</v>
       </c>
+      <c r="E549" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -10331,6 +11980,9 @@
       <c r="D550" t="n">
         <v>3</v>
       </c>
+      <c r="E550" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -10349,6 +12001,9 @@
       <c r="D551" t="n">
         <v>2</v>
       </c>
+      <c r="E551" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -10367,6 +12022,9 @@
       <c r="D552" t="n">
         <v>2</v>
       </c>
+      <c r="E552" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -10385,6 +12043,9 @@
       <c r="D553" t="n">
         <v>2</v>
       </c>
+      <c r="E553" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -10403,6 +12064,9 @@
       <c r="D554" t="n">
         <v>3</v>
       </c>
+      <c r="E554" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -10421,6 +12085,9 @@
       <c r="D555" t="n">
         <v>2</v>
       </c>
+      <c r="E555" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -10439,6 +12106,9 @@
       <c r="D556" t="n">
         <v>2</v>
       </c>
+      <c r="E556" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -10457,6 +12127,9 @@
       <c r="D557" t="n">
         <v>3</v>
       </c>
+      <c r="E557" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -10475,6 +12148,9 @@
       <c r="D558" t="n">
         <v>1</v>
       </c>
+      <c r="E558" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -10493,6 +12169,9 @@
       <c r="D559" t="n">
         <v>1</v>
       </c>
+      <c r="E559" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -10511,6 +12190,9 @@
       <c r="D560" t="n">
         <v>1</v>
       </c>
+      <c r="E560" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -10529,6 +12211,9 @@
       <c r="D561" t="n">
         <v>0</v>
       </c>
+      <c r="E561" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -10547,6 +12232,9 @@
       <c r="D562" t="n">
         <v>2</v>
       </c>
+      <c r="E562" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -10565,6 +12253,9 @@
       <c r="D563" t="n">
         <v>2</v>
       </c>
+      <c r="E563" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -10583,6 +12274,9 @@
       <c r="D564" t="n">
         <v>1</v>
       </c>
+      <c r="E564" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -10601,6 +12295,9 @@
       <c r="D565" t="n">
         <v>1</v>
       </c>
+      <c r="E565" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -10619,6 +12316,9 @@
       <c r="D566" t="n">
         <v>0</v>
       </c>
+      <c r="E566" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -10637,6 +12337,9 @@
       <c r="D567" t="n">
         <v>0</v>
       </c>
+      <c r="E567" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -10655,6 +12358,9 @@
       <c r="D568" t="n">
         <v>0</v>
       </c>
+      <c r="E568" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -10673,6 +12379,9 @@
       <c r="D569" t="n">
         <v>0</v>
       </c>
+      <c r="E569" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -10691,6 +12400,9 @@
       <c r="D570" t="n">
         <v>3</v>
       </c>
+      <c r="E570" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -10709,6 +12421,9 @@
       <c r="D571" t="n">
         <v>3</v>
       </c>
+      <c r="E571" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -10727,6 +12442,9 @@
       <c r="D572" t="n">
         <v>2</v>
       </c>
+      <c r="E572" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -10745,6 +12463,9 @@
       <c r="D573" t="n">
         <v>2</v>
       </c>
+      <c r="E573" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -10763,6 +12484,9 @@
       <c r="D574" t="n">
         <v>2</v>
       </c>
+      <c r="E574" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -10781,6 +12505,9 @@
       <c r="D575" t="n">
         <v>2</v>
       </c>
+      <c r="E575" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -10799,6 +12526,9 @@
       <c r="D576" t="n">
         <v>2</v>
       </c>
+      <c r="E576" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -10817,6 +12547,9 @@
       <c r="D577" t="n">
         <v>2</v>
       </c>
+      <c r="E577" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -10835,6 +12568,9 @@
       <c r="D578" t="n">
         <v>2</v>
       </c>
+      <c r="E578" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -10853,6 +12589,9 @@
       <c r="D579" t="n">
         <v>2</v>
       </c>
+      <c r="E579" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -10871,6 +12610,9 @@
       <c r="D580" t="n">
         <v>2</v>
       </c>
+      <c r="E580" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -10889,6 +12631,9 @@
       <c r="D581" t="n">
         <v>2</v>
       </c>
+      <c r="E581" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -10907,6 +12652,9 @@
       <c r="D582" t="n">
         <v>2</v>
       </c>
+      <c r="E582" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -10925,6 +12673,9 @@
       <c r="D583" t="n">
         <v>2</v>
       </c>
+      <c r="E583" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -10943,6 +12694,9 @@
       <c r="D584" t="n">
         <v>3</v>
       </c>
+      <c r="E584" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -10961,6 +12715,9 @@
       <c r="D585" t="n">
         <v>2</v>
       </c>
+      <c r="E585" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -10979,6 +12736,9 @@
       <c r="D586" t="n">
         <v>1</v>
       </c>
+      <c r="E586" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -10997,6 +12757,9 @@
       <c r="D587" t="n">
         <v>2</v>
       </c>
+      <c r="E587" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -11015,6 +12778,9 @@
       <c r="D588" t="n">
         <v>1</v>
       </c>
+      <c r="E588" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -11033,6 +12799,9 @@
       <c r="D589" t="n">
         <v>1</v>
       </c>
+      <c r="E589" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -11051,6 +12820,9 @@
       <c r="D590" t="n">
         <v>1</v>
       </c>
+      <c r="E590" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -11069,6 +12841,9 @@
       <c r="D591" t="n">
         <v>1</v>
       </c>
+      <c r="E591" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -11087,6 +12862,9 @@
       <c r="D592" t="n">
         <v>1</v>
       </c>
+      <c r="E592" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -11105,6 +12883,9 @@
       <c r="D593" t="n">
         <v>1</v>
       </c>
+      <c r="E593" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -11123,6 +12904,9 @@
       <c r="D594" t="n">
         <v>1</v>
       </c>
+      <c r="E594" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -11141,6 +12925,9 @@
       <c r="D595" t="n">
         <v>1</v>
       </c>
+      <c r="E595" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -11159,6 +12946,9 @@
       <c r="D596" t="n">
         <v>2</v>
       </c>
+      <c r="E596" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -11177,6 +12967,9 @@
       <c r="D597" t="n">
         <v>2</v>
       </c>
+      <c r="E597" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -11195,6 +12988,9 @@
       <c r="D598" t="n">
         <v>1</v>
       </c>
+      <c r="E598" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -11213,6 +13009,9 @@
       <c r="D599" t="n">
         <v>1</v>
       </c>
+      <c r="E599" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -11231,6 +13030,9 @@
       <c r="D600" t="n">
         <v>2</v>
       </c>
+      <c r="E600" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -11249,6 +13051,9 @@
       <c r="D601" t="n">
         <v>2</v>
       </c>
+      <c r="E601" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -11267,6 +13072,9 @@
       <c r="D602" t="n">
         <v>1</v>
       </c>
+      <c r="E602" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -11285,6 +13093,9 @@
       <c r="D603" t="n">
         <v>1</v>
       </c>
+      <c r="E603" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -11303,6 +13114,9 @@
       <c r="D604" t="n">
         <v>1</v>
       </c>
+      <c r="E604" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -11321,6 +13135,9 @@
       <c r="D605" t="n">
         <v>2</v>
       </c>
+      <c r="E605" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -11339,6 +13156,9 @@
       <c r="D606" t="n">
         <v>2</v>
       </c>
+      <c r="E606" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -11357,6 +13177,9 @@
       <c r="D607" t="n">
         <v>2</v>
       </c>
+      <c r="E607" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -11375,6 +13198,9 @@
       <c r="D608" t="n">
         <v>1</v>
       </c>
+      <c r="E608" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -11393,6 +13219,9 @@
       <c r="D609" t="n">
         <v>1</v>
       </c>
+      <c r="E609" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -11411,6 +13240,9 @@
       <c r="D610" t="n">
         <v>1</v>
       </c>
+      <c r="E610" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -11429,6 +13261,9 @@
       <c r="D611" t="n">
         <v>1</v>
       </c>
+      <c r="E611" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -11447,6 +13282,9 @@
       <c r="D612" t="n">
         <v>3</v>
       </c>
+      <c r="E612" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -11465,6 +13303,9 @@
       <c r="D613" t="n">
         <v>1</v>
       </c>
+      <c r="E613" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -11483,6 +13324,9 @@
       <c r="D614" t="n">
         <v>1</v>
       </c>
+      <c r="E614" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -11501,6 +13345,9 @@
       <c r="D615" t="n">
         <v>2</v>
       </c>
+      <c r="E615" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -11519,6 +13366,9 @@
       <c r="D616" t="n">
         <v>2</v>
       </c>
+      <c r="E616" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -11537,6 +13387,9 @@
       <c r="D617" t="n">
         <v>3</v>
       </c>
+      <c r="E617" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -11555,6 +13408,9 @@
       <c r="D618" t="n">
         <v>3</v>
       </c>
+      <c r="E618" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -11573,6 +13429,9 @@
       <c r="D619" t="n">
         <v>3</v>
       </c>
+      <c r="E619" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -11591,6 +13450,9 @@
       <c r="D620" t="n">
         <v>3</v>
       </c>
+      <c r="E620" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -11609,6 +13471,9 @@
       <c r="D621" t="n">
         <v>2</v>
       </c>
+      <c r="E621" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -11627,6 +13492,9 @@
       <c r="D622" t="n">
         <v>2</v>
       </c>
+      <c r="E622" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -11645,6 +13513,9 @@
       <c r="D623" t="n">
         <v>1</v>
       </c>
+      <c r="E623" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -11663,6 +13534,9 @@
       <c r="D624" t="n">
         <v>2</v>
       </c>
+      <c r="E624" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -11681,6 +13555,9 @@
       <c r="D625" t="n">
         <v>2</v>
       </c>
+      <c r="E625" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -11699,6 +13576,9 @@
       <c r="D626" t="n">
         <v>2</v>
       </c>
+      <c r="E626" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -11717,6 +13597,9 @@
       <c r="D627" t="n">
         <v>2</v>
       </c>
+      <c r="E627" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -11735,6 +13618,9 @@
       <c r="D628" t="n">
         <v>2</v>
       </c>
+      <c r="E628" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -11753,6 +13639,9 @@
       <c r="D629" t="n">
         <v>2</v>
       </c>
+      <c r="E629" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -11771,6 +13660,9 @@
       <c r="D630" t="n">
         <v>2</v>
       </c>
+      <c r="E630" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -11789,6 +13681,9 @@
       <c r="D631" t="n">
         <v>1</v>
       </c>
+      <c r="E631" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -11807,6 +13702,9 @@
       <c r="D632" t="n">
         <v>0</v>
       </c>
+      <c r="E632" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -11825,6 +13723,9 @@
       <c r="D633" t="n">
         <v>1</v>
       </c>
+      <c r="E633" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -11843,6 +13744,9 @@
       <c r="D634" t="n">
         <v>1</v>
       </c>
+      <c r="E634" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -11861,6 +13765,9 @@
       <c r="D635" t="n">
         <v>1</v>
       </c>
+      <c r="E635" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -11879,6 +13786,9 @@
       <c r="D636" t="n">
         <v>1</v>
       </c>
+      <c r="E636" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -11897,6 +13807,9 @@
       <c r="D637" t="n">
         <v>1</v>
       </c>
+      <c r="E637" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -11915,6 +13828,9 @@
       <c r="D638" t="n">
         <v>0</v>
       </c>
+      <c r="E638" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -11933,6 +13849,9 @@
       <c r="D639" t="n">
         <v>2</v>
       </c>
+      <c r="E639" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -11951,6 +13870,9 @@
       <c r="D640" t="n">
         <v>2</v>
       </c>
+      <c r="E640" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -11969,6 +13891,9 @@
       <c r="D641" t="n">
         <v>2</v>
       </c>
+      <c r="E641" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -11987,6 +13912,9 @@
       <c r="D642" t="n">
         <v>2</v>
       </c>
+      <c r="E642" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -12005,6 +13933,9 @@
       <c r="D643" t="n">
         <v>2</v>
       </c>
+      <c r="E643" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -12023,6 +13954,9 @@
       <c r="D644" t="n">
         <v>1</v>
       </c>
+      <c r="E644" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -12041,6 +13975,9 @@
       <c r="D645" t="n">
         <v>1</v>
       </c>
+      <c r="E645" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -12059,6 +13996,9 @@
       <c r="D646" t="n">
         <v>1</v>
       </c>
+      <c r="E646" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -12077,6 +14017,9 @@
       <c r="D647" t="n">
         <v>0</v>
       </c>
+      <c r="E647" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -12095,6 +14038,9 @@
       <c r="D648" t="n">
         <v>0</v>
       </c>
+      <c r="E648" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -12113,6 +14059,9 @@
       <c r="D649" t="n">
         <v>0</v>
       </c>
+      <c r="E649" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -12131,6 +14080,9 @@
       <c r="D650" t="n">
         <v>0</v>
       </c>
+      <c r="E650" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -12149,6 +14101,9 @@
       <c r="D651" t="n">
         <v>0</v>
       </c>
+      <c r="E651" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -12167,6 +14122,9 @@
       <c r="D652" t="n">
         <v>0</v>
       </c>
+      <c r="E652" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -12185,6 +14143,9 @@
       <c r="D653" t="n">
         <v>0</v>
       </c>
+      <c r="E653" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -12203,6 +14164,9 @@
       <c r="D654" t="n">
         <v>0</v>
       </c>
+      <c r="E654" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -12221,6 +14185,9 @@
       <c r="D655" t="n">
         <v>0</v>
       </c>
+      <c r="E655" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -12239,6 +14206,9 @@
       <c r="D656" t="n">
         <v>0</v>
       </c>
+      <c r="E656" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -12257,6 +14227,9 @@
       <c r="D657" t="n">
         <v>0</v>
       </c>
+      <c r="E657" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -12275,6 +14248,9 @@
       <c r="D658" t="n">
         <v>0</v>
       </c>
+      <c r="E658" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -12293,6 +14269,9 @@
       <c r="D659" t="n">
         <v>0</v>
       </c>
+      <c r="E659" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -12311,6 +14290,9 @@
       <c r="D660" t="n">
         <v>0</v>
       </c>
+      <c r="E660" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -12329,6 +14311,9 @@
       <c r="D661" t="n">
         <v>1</v>
       </c>
+      <c r="E661" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -12347,6 +14332,9 @@
       <c r="D662" t="n">
         <v>1</v>
       </c>
+      <c r="E662" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -12365,6 +14353,9 @@
       <c r="D663" t="n">
         <v>1</v>
       </c>
+      <c r="E663" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -12383,6 +14374,9 @@
       <c r="D664" t="n">
         <v>1</v>
       </c>
+      <c r="E664" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -12401,6 +14395,9 @@
       <c r="D665" t="n">
         <v>1</v>
       </c>
+      <c r="E665" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -12419,6 +14416,9 @@
       <c r="D666" t="n">
         <v>1</v>
       </c>
+      <c r="E666" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -12437,6 +14437,9 @@
       <c r="D667" t="n">
         <v>1</v>
       </c>
+      <c r="E667" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -12455,6 +14458,9 @@
       <c r="D668" t="n">
         <v>1</v>
       </c>
+      <c r="E668" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -12473,6 +14479,9 @@
       <c r="D669" t="n">
         <v>1</v>
       </c>
+      <c r="E669" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -12491,6 +14500,9 @@
       <c r="D670" t="n">
         <v>0</v>
       </c>
+      <c r="E670" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -12509,6 +14521,9 @@
       <c r="D671" t="n">
         <v>0</v>
       </c>
+      <c r="E671" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -12527,6 +14542,9 @@
       <c r="D672" t="n">
         <v>0</v>
       </c>
+      <c r="E672" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -12545,6 +14563,9 @@
       <c r="D673" t="n">
         <v>0</v>
       </c>
+      <c r="E673" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -12563,6 +14584,9 @@
       <c r="D674" t="n">
         <v>0</v>
       </c>
+      <c r="E674" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -12581,6 +14605,9 @@
       <c r="D675" t="n">
         <v>0</v>
       </c>
+      <c r="E675" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -12599,6 +14626,9 @@
       <c r="D676" t="n">
         <v>0</v>
       </c>
+      <c r="E676" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -12617,6 +14647,9 @@
       <c r="D677" t="n">
         <v>0</v>
       </c>
+      <c r="E677" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -12635,6 +14668,9 @@
       <c r="D678" t="n">
         <v>0</v>
       </c>
+      <c r="E678" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -12653,6 +14689,9 @@
       <c r="D679" t="n">
         <v>0</v>
       </c>
+      <c r="E679" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -12671,6 +14710,9 @@
       <c r="D680" t="n">
         <v>0</v>
       </c>
+      <c r="E680" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -12689,6 +14731,9 @@
       <c r="D681" t="n">
         <v>0</v>
       </c>
+      <c r="E681" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -12707,6 +14752,9 @@
       <c r="D682" t="n">
         <v>0</v>
       </c>
+      <c r="E682" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -12725,6 +14773,9 @@
       <c r="D683" t="n">
         <v>0</v>
       </c>
+      <c r="E683" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -12743,6 +14794,9 @@
       <c r="D684" t="n">
         <v>0</v>
       </c>
+      <c r="E684" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -12761,6 +14815,9 @@
       <c r="D685" t="n">
         <v>0</v>
       </c>
+      <c r="E685" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -12779,6 +14836,9 @@
       <c r="D686" t="n">
         <v>0</v>
       </c>
+      <c r="E686" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -12797,6 +14857,9 @@
       <c r="D687" t="n">
         <v>1</v>
       </c>
+      <c r="E687" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -12815,6 +14878,9 @@
       <c r="D688" t="n">
         <v>1</v>
       </c>
+      <c r="E688" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -12833,6 +14899,9 @@
       <c r="D689" t="n">
         <v>1</v>
       </c>
+      <c r="E689" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -12851,6 +14920,9 @@
       <c r="D690" t="n">
         <v>2</v>
       </c>
+      <c r="E690" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -12869,6 +14941,9 @@
       <c r="D691" t="n">
         <v>2</v>
       </c>
+      <c r="E691" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -12887,6 +14962,9 @@
       <c r="D692" t="n">
         <v>2</v>
       </c>
+      <c r="E692" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -12905,6 +14983,9 @@
       <c r="D693" t="n">
         <v>2</v>
       </c>
+      <c r="E693" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -12923,6 +15004,9 @@
       <c r="D694" t="n">
         <v>1</v>
       </c>
+      <c r="E694" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -12941,6 +15025,9 @@
       <c r="D695" t="n">
         <v>1</v>
       </c>
+      <c r="E695" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -12959,6 +15046,9 @@
       <c r="D696" t="n">
         <v>3</v>
       </c>
+      <c r="E696" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -12977,6 +15067,9 @@
       <c r="D697" t="n">
         <v>1</v>
       </c>
+      <c r="E697" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -12995,6 +15088,9 @@
       <c r="D698" t="n">
         <v>1</v>
       </c>
+      <c r="E698" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -13013,6 +15109,9 @@
       <c r="D699" t="n">
         <v>1</v>
       </c>
+      <c r="E699" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -13031,6 +15130,9 @@
       <c r="D700" t="n">
         <v>1</v>
       </c>
+      <c r="E700" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -13049,6 +15151,9 @@
       <c r="D701" t="n">
         <v>1</v>
       </c>
+      <c r="E701" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -13067,6 +15172,9 @@
       <c r="D702" t="n">
         <v>0</v>
       </c>
+      <c r="E702" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -13085,6 +15193,9 @@
       <c r="D703" t="n">
         <v>0</v>
       </c>
+      <c r="E703" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -13103,6 +15214,9 @@
       <c r="D704" t="n">
         <v>0</v>
       </c>
+      <c r="E704" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -13121,6 +15235,9 @@
       <c r="D705" t="n">
         <v>0</v>
       </c>
+      <c r="E705" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -13139,6 +15256,9 @@
       <c r="D706" t="n">
         <v>0</v>
       </c>
+      <c r="E706" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -13157,6 +15277,9 @@
       <c r="D707" t="n">
         <v>0</v>
       </c>
+      <c r="E707" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -13175,6 +15298,9 @@
       <c r="D708" t="n">
         <v>0</v>
       </c>
+      <c r="E708" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -13193,6 +15319,9 @@
       <c r="D709" t="n">
         <v>0</v>
       </c>
+      <c r="E709" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -13211,6 +15340,9 @@
       <c r="D710" t="n">
         <v>0</v>
       </c>
+      <c r="E710" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -13229,6 +15361,9 @@
       <c r="D711" t="n">
         <v>3</v>
       </c>
+      <c r="E711" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -13246,6 +15381,9 @@
       </c>
       <c r="D712" t="n">
         <v>4</v>
+      </c>
+      <c r="E712" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/bonncohort/info_bonn_cohort.xlsx
+++ b/results/bonncohort/info_bonn_cohort.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>EZ_as_exported</t>
+          <t>EZ_in_export</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -557,7 +557,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -599,7 +599,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -620,7 +620,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -662,7 +662,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -683,7 +683,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -725,7 +725,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -746,7 +746,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -767,7 +767,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -788,7 +788,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -809,7 +809,7 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -851,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -914,7 +914,7 @@
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -956,7 +956,7 @@
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -977,7 +977,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -998,7 +998,7 @@
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1040,7 +1040,7 @@
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1061,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1082,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1124,7 +1124,7 @@
         <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1145,7 +1145,7 @@
         <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1166,7 +1166,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1187,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1229,7 +1229,7 @@
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1250,7 +1250,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1292,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1313,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1355,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1376,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1397,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1418,7 +1418,7 @@
         <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1439,7 +1439,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1460,7 +1460,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1481,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1502,7 +1502,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1523,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1544,7 +1544,7 @@
         <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1565,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1586,7 +1586,7 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1649,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1670,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1691,7 +1691,7 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1712,7 +1712,7 @@
         <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -1733,7 +1733,7 @@
         <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -1754,7 +1754,7 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -1775,7 +1775,7 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -1796,7 +1796,7 @@
         <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -1817,7 +1817,7 @@
         <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -1838,7 +1838,7 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -1859,7 +1859,7 @@
         <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -1880,7 +1880,7 @@
         <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -1901,7 +1901,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -1922,7 +1922,7 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -1943,7 +1943,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -1964,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2069,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2153,7 +2153,7 @@
         <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2174,7 +2174,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2195,7 +2195,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2216,7 +2216,7 @@
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2237,7 +2237,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2342,7 +2342,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2363,7 +2363,7 @@
         <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -2384,7 +2384,7 @@
         <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2405,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2468,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -2489,7 +2489,7 @@
         <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -2531,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2552,7 +2552,7 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2657,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -2678,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -2699,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -2720,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -2825,7 +2825,7 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -2867,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -2888,7 +2888,7 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -2909,7 +2909,7 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -2930,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -2972,7 +2972,7 @@
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -3077,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -3161,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3182,7 +3182,7 @@
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3224,7 +3224,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3245,7 +3245,7 @@
         <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3287,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -3308,7 +3308,7 @@
         <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -3350,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -3371,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3434,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -3455,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -3560,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -3581,7 +3581,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -3623,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -3707,7 +3707,7 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -4232,7 +4232,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4253,7 +4253,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4274,7 +4274,7 @@
         <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4295,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -4820,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -4841,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -4967,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -5114,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -5135,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -5177,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -5387,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="E236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -5429,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -5471,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -5492,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -5513,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -5534,7 +5534,7 @@
         <v>2</v>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -5576,7 +5576,7 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -5597,7 +5597,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -5618,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -5849,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -5870,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -5891,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -6101,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -6122,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -6437,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="E286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -6479,7 +6479,7 @@
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -6521,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="E290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -6542,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="E291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -6710,7 +6710,7 @@
         <v>1</v>
       </c>
       <c r="E299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
@@ -6878,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="E307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -6899,7 +6899,7 @@
         <v>2</v>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
@@ -6920,7 +6920,7 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -6941,7 +6941,7 @@
         <v>3</v>
       </c>
       <c r="E310" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -6962,7 +6962,7 @@
         <v>3</v>
       </c>
       <c r="E311" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -6983,7 +6983,7 @@
         <v>2</v>
       </c>
       <c r="E312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -7004,7 +7004,7 @@
         <v>2</v>
       </c>
       <c r="E313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -7025,7 +7025,7 @@
         <v>3</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -7046,7 +7046,7 @@
         <v>2</v>
       </c>
       <c r="E315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -7067,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="E316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -7088,7 +7088,7 @@
         <v>3</v>
       </c>
       <c r="E317" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -7109,7 +7109,7 @@
         <v>2</v>
       </c>
       <c r="E318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -7130,7 +7130,7 @@
         <v>2</v>
       </c>
       <c r="E319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -7151,7 +7151,7 @@
         <v>2</v>
       </c>
       <c r="E320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -7172,7 +7172,7 @@
         <v>2</v>
       </c>
       <c r="E321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -7193,7 +7193,7 @@
         <v>2</v>
       </c>
       <c r="E322" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323">
@@ -7214,7 +7214,7 @@
         <v>2</v>
       </c>
       <c r="E323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -7235,7 +7235,7 @@
         <v>2</v>
       </c>
       <c r="E324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -7256,7 +7256,7 @@
         <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -7277,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="E326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -7298,7 +7298,7 @@
         <v>3</v>
       </c>
       <c r="E327" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -7319,7 +7319,7 @@
         <v>4</v>
       </c>
       <c r="E328" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="329">
@@ -7340,7 +7340,7 @@
         <v>3</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -7361,7 +7361,7 @@
         <v>3</v>
       </c>
       <c r="E330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -7382,7 +7382,7 @@
         <v>2</v>
       </c>
       <c r="E331" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -7403,7 +7403,7 @@
         <v>1</v>
       </c>
       <c r="E332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -7445,7 +7445,7 @@
         <v>1</v>
       </c>
       <c r="E334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -7466,7 +7466,7 @@
         <v>4</v>
       </c>
       <c r="E335" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="336">
@@ -7487,7 +7487,7 @@
         <v>4</v>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="337">
@@ -7508,7 +7508,7 @@
         <v>3</v>
       </c>
       <c r="E337" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
@@ -7529,7 +7529,7 @@
         <v>2</v>
       </c>
       <c r="E338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -7865,7 +7865,7 @@
         <v>2</v>
       </c>
       <c r="E354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -7928,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="E357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -7949,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="E358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
@@ -7970,7 +7970,7 @@
         <v>1</v>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -7991,7 +7991,7 @@
         <v>2</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -8012,7 +8012,7 @@
         <v>3</v>
       </c>
       <c r="E361" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -8033,7 +8033,7 @@
         <v>2</v>
       </c>
       <c r="E362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -8054,7 +8054,7 @@
         <v>2</v>
       </c>
       <c r="E363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -8075,7 +8075,7 @@
         <v>2</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -8096,7 +8096,7 @@
         <v>2</v>
       </c>
       <c r="E365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -8117,7 +8117,7 @@
         <v>1</v>
       </c>
       <c r="E366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -8159,7 +8159,7 @@
         <v>3</v>
       </c>
       <c r="E368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -8180,7 +8180,7 @@
         <v>4</v>
       </c>
       <c r="E369" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="370">
@@ -8201,7 +8201,7 @@
         <v>2</v>
       </c>
       <c r="E370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -8222,7 +8222,7 @@
         <v>1</v>
       </c>
       <c r="E371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
@@ -8243,7 +8243,7 @@
         <v>3</v>
       </c>
       <c r="E372" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -8264,7 +8264,7 @@
         <v>2</v>
       </c>
       <c r="E373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -8285,7 +8285,7 @@
         <v>3</v>
       </c>
       <c r="E374" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
@@ -8306,7 +8306,7 @@
         <v>1</v>
       </c>
       <c r="E375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8327,7 +8327,7 @@
         <v>2</v>
       </c>
       <c r="E376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
@@ -8348,7 +8348,7 @@
         <v>2</v>
       </c>
       <c r="E377" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378">
@@ -8390,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="E379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -8411,7 +8411,7 @@
         <v>2</v>
       </c>
       <c r="E380" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="381">
@@ -8432,7 +8432,7 @@
         <v>3</v>
       </c>
       <c r="E381" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -8453,7 +8453,7 @@
         <v>1</v>
       </c>
       <c r="E382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -8474,7 +8474,7 @@
         <v>3</v>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -8495,7 +8495,7 @@
         <v>2</v>
       </c>
       <c r="E384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -8516,7 +8516,7 @@
         <v>3</v>
       </c>
       <c r="E385" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -8579,7 +8579,7 @@
         <v>1</v>
       </c>
       <c r="E388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
@@ -8600,7 +8600,7 @@
         <v>2</v>
       </c>
       <c r="E389" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -8621,7 +8621,7 @@
         <v>2</v>
       </c>
       <c r="E390" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -8663,7 +8663,7 @@
         <v>1</v>
       </c>
       <c r="E392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -8684,7 +8684,7 @@
         <v>2</v>
       </c>
       <c r="E393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="394">
@@ -8705,7 +8705,7 @@
         <v>3</v>
       </c>
       <c r="E394" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -8726,7 +8726,7 @@
         <v>3</v>
       </c>
       <c r="E395" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -8747,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="E396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -8768,7 +8768,7 @@
         <v>1</v>
       </c>
       <c r="E397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -8789,7 +8789,7 @@
         <v>1</v>
       </c>
       <c r="E398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
@@ -8831,7 +8831,7 @@
         <v>2</v>
       </c>
       <c r="E400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="401">
@@ -8852,7 +8852,7 @@
         <v>1</v>
       </c>
       <c r="E401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402">
@@ -8978,7 +8978,7 @@
         <v>2</v>
       </c>
       <c r="E407" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -8999,7 +8999,7 @@
         <v>2</v>
       </c>
       <c r="E408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -9020,7 +9020,7 @@
         <v>2</v>
       </c>
       <c r="E409" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -9041,7 +9041,7 @@
         <v>1</v>
       </c>
       <c r="E410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -9167,7 +9167,7 @@
         <v>1</v>
       </c>
       <c r="E416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -9230,7 +9230,7 @@
         <v>2</v>
       </c>
       <c r="E419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -9251,7 +9251,7 @@
         <v>1</v>
       </c>
       <c r="E420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9272,7 +9272,7 @@
         <v>2</v>
       </c>
       <c r="E421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -9293,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="E422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -9314,7 +9314,7 @@
         <v>2</v>
       </c>
       <c r="E423" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="424">
@@ -9335,7 +9335,7 @@
         <v>2</v>
       </c>
       <c r="E424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="425">
@@ -9356,7 +9356,7 @@
         <v>2</v>
       </c>
       <c r="E425" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="426">
@@ -9377,7 +9377,7 @@
         <v>3</v>
       </c>
       <c r="E426" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -9398,7 +9398,7 @@
         <v>3</v>
       </c>
       <c r="E427" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -9419,7 +9419,7 @@
         <v>2</v>
       </c>
       <c r="E428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -9440,7 +9440,7 @@
         <v>2</v>
       </c>
       <c r="E429" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -9461,7 +9461,7 @@
         <v>3</v>
       </c>
       <c r="E430" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -9482,7 +9482,7 @@
         <v>3</v>
       </c>
       <c r="E431" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -9503,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="E432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9524,7 +9524,7 @@
         <v>2</v>
       </c>
       <c r="E433" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -9545,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="E434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -9587,7 +9587,7 @@
         <v>2</v>
       </c>
       <c r="E436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -9608,7 +9608,7 @@
         <v>1</v>
       </c>
       <c r="E437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -9629,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="E438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9650,7 +9650,7 @@
         <v>1</v>
       </c>
       <c r="E439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
@@ -9671,7 +9671,7 @@
         <v>1</v>
       </c>
       <c r="E440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -9692,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="E441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -9713,7 +9713,7 @@
         <v>1</v>
       </c>
       <c r="E442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -9734,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="E443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444">
@@ -9776,7 +9776,7 @@
         <v>1</v>
       </c>
       <c r="E445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -9797,7 +9797,7 @@
         <v>1</v>
       </c>
       <c r="E446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -9902,7 +9902,7 @@
         <v>1</v>
       </c>
       <c r="E451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -9944,7 +9944,7 @@
         <v>2</v>
       </c>
       <c r="E453" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -9965,7 +9965,7 @@
         <v>1</v>
       </c>
       <c r="E454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -9986,7 +9986,7 @@
         <v>2</v>
       </c>
       <c r="E455" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -10007,7 +10007,7 @@
         <v>2</v>
       </c>
       <c r="E456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -10028,7 +10028,7 @@
         <v>2</v>
       </c>
       <c r="E457" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -10049,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="E458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -10070,7 +10070,7 @@
         <v>3</v>
       </c>
       <c r="E459" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -10091,7 +10091,7 @@
         <v>5</v>
       </c>
       <c r="E460" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="461">
@@ -10112,7 +10112,7 @@
         <v>2</v>
       </c>
       <c r="E461" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -10133,7 +10133,7 @@
         <v>3</v>
       </c>
       <c r="E462" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -10154,7 +10154,7 @@
         <v>2</v>
       </c>
       <c r="E463" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -10175,7 +10175,7 @@
         <v>3</v>
       </c>
       <c r="E464" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -10196,7 +10196,7 @@
         <v>3</v>
       </c>
       <c r="E465" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -10217,7 +10217,7 @@
         <v>2</v>
       </c>
       <c r="E466" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -10238,7 +10238,7 @@
         <v>4</v>
       </c>
       <c r="E467" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="468">
@@ -10259,7 +10259,7 @@
         <v>3</v>
       </c>
       <c r="E468" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="469">
@@ -10280,7 +10280,7 @@
         <v>3</v>
       </c>
       <c r="E469" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="470">
@@ -10301,7 +10301,7 @@
         <v>2</v>
       </c>
       <c r="E470" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="471">
@@ -10322,7 +10322,7 @@
         <v>2</v>
       </c>
       <c r="E471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="472">
@@ -10343,7 +10343,7 @@
         <v>1</v>
       </c>
       <c r="E472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -10364,7 +10364,7 @@
         <v>2</v>
       </c>
       <c r="E473" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -10385,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="E474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -10406,7 +10406,7 @@
         <v>1</v>
       </c>
       <c r="E475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -10427,7 +10427,7 @@
         <v>2</v>
       </c>
       <c r="E476" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -10448,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="E477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -10469,7 +10469,7 @@
         <v>1</v>
       </c>
       <c r="E478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -10490,7 +10490,7 @@
         <v>1</v>
       </c>
       <c r="E479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -10511,7 +10511,7 @@
         <v>1</v>
       </c>
       <c r="E480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -10532,7 +10532,7 @@
         <v>1</v>
       </c>
       <c r="E481" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -10553,7 +10553,7 @@
         <v>1</v>
       </c>
       <c r="E482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -10574,7 +10574,7 @@
         <v>1</v>
       </c>
       <c r="E483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -10616,7 +10616,7 @@
         <v>1</v>
       </c>
       <c r="E485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486">
@@ -10637,7 +10637,7 @@
         <v>1</v>
       </c>
       <c r="E486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
@@ -10658,7 +10658,7 @@
         <v>3</v>
       </c>
       <c r="E487" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -10679,7 +10679,7 @@
         <v>3</v>
       </c>
       <c r="E488" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
@@ -10700,7 +10700,7 @@
         <v>2</v>
       </c>
       <c r="E489" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -10721,7 +10721,7 @@
         <v>2</v>
       </c>
       <c r="E490" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -10742,7 +10742,7 @@
         <v>3</v>
       </c>
       <c r="E491" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -10763,7 +10763,7 @@
         <v>3</v>
       </c>
       <c r="E492" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -10784,7 +10784,7 @@
         <v>2</v>
       </c>
       <c r="E493" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -10805,7 +10805,7 @@
         <v>3</v>
       </c>
       <c r="E494" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -10826,7 +10826,7 @@
         <v>4</v>
       </c>
       <c r="E495" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="496">
@@ -10847,7 +10847,7 @@
         <v>2</v>
       </c>
       <c r="E496" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -10868,7 +10868,7 @@
         <v>2</v>
       </c>
       <c r="E497" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -10889,7 +10889,7 @@
         <v>3</v>
       </c>
       <c r="E498" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -10910,7 +10910,7 @@
         <v>4</v>
       </c>
       <c r="E499" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="500">
@@ -10931,7 +10931,7 @@
         <v>3</v>
       </c>
       <c r="E500" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -10952,7 +10952,7 @@
         <v>4</v>
       </c>
       <c r="E501" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="502">
@@ -10973,7 +10973,7 @@
         <v>6</v>
       </c>
       <c r="E502" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="503">
@@ -10994,7 +10994,7 @@
         <v>7</v>
       </c>
       <c r="E503" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="504">
@@ -11015,7 +11015,7 @@
         <v>2</v>
       </c>
       <c r="E504" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -11036,7 +11036,7 @@
         <v>1</v>
       </c>
       <c r="E505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -11120,7 +11120,7 @@
         <v>1</v>
       </c>
       <c r="E509" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -11141,7 +11141,7 @@
         <v>2</v>
       </c>
       <c r="E510" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
@@ -11162,7 +11162,7 @@
         <v>2</v>
       </c>
       <c r="E511" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512">
@@ -11246,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="E515" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516">
@@ -11309,7 +11309,7 @@
         <v>3</v>
       </c>
       <c r="E518" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="519">
@@ -11330,7 +11330,7 @@
         <v>1</v>
       </c>
       <c r="E519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520">
@@ -11351,7 +11351,7 @@
         <v>3</v>
       </c>
       <c r="E520" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521">
@@ -11372,7 +11372,7 @@
         <v>2</v>
       </c>
       <c r="E521" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -11393,7 +11393,7 @@
         <v>2</v>
       </c>
       <c r="E522" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="523">
@@ -11414,7 +11414,7 @@
         <v>3</v>
       </c>
       <c r="E523" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524">
@@ -11435,7 +11435,7 @@
         <v>2</v>
       </c>
       <c r="E524" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -11456,7 +11456,7 @@
         <v>3</v>
       </c>
       <c r="E525" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="526">
@@ -11477,7 +11477,7 @@
         <v>3</v>
       </c>
       <c r="E526" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="527">
@@ -11498,7 +11498,7 @@
         <v>3</v>
       </c>
       <c r="E527" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -11519,7 +11519,7 @@
         <v>3</v>
       </c>
       <c r="E528" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -11540,7 +11540,7 @@
         <v>3</v>
       </c>
       <c r="E529" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="530">
@@ -11561,7 +11561,7 @@
         <v>3</v>
       </c>
       <c r="E530" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -11582,7 +11582,7 @@
         <v>3</v>
       </c>
       <c r="E531" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -11603,7 +11603,7 @@
         <v>2</v>
       </c>
       <c r="E532" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -11624,7 +11624,7 @@
         <v>2</v>
       </c>
       <c r="E533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -11645,7 +11645,7 @@
         <v>2</v>
       </c>
       <c r="E534" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -11666,7 +11666,7 @@
         <v>3</v>
       </c>
       <c r="E535" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -11687,7 +11687,7 @@
         <v>2</v>
       </c>
       <c r="E536" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -11708,7 +11708,7 @@
         <v>2</v>
       </c>
       <c r="E537" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -11729,7 +11729,7 @@
         <v>2</v>
       </c>
       <c r="E538" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -11771,7 +11771,7 @@
         <v>2</v>
       </c>
       <c r="E540" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -11792,7 +11792,7 @@
         <v>1</v>
       </c>
       <c r="E541" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542">
@@ -11813,7 +11813,7 @@
         <v>1</v>
       </c>
       <c r="E542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
@@ -11834,7 +11834,7 @@
         <v>1</v>
       </c>
       <c r="E543" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
@@ -11855,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="E544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -11876,7 +11876,7 @@
         <v>1</v>
       </c>
       <c r="E545" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
@@ -11897,7 +11897,7 @@
         <v>1</v>
       </c>
       <c r="E546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -11918,7 +11918,7 @@
         <v>2</v>
       </c>
       <c r="E547" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="548">
@@ -11939,7 +11939,7 @@
         <v>2</v>
       </c>
       <c r="E548" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549">
@@ -11960,7 +11960,7 @@
         <v>3</v>
       </c>
       <c r="E549" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="550">
@@ -11981,7 +11981,7 @@
         <v>3</v>
       </c>
       <c r="E550" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="551">
@@ -12002,7 +12002,7 @@
         <v>2</v>
       </c>
       <c r="E551" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -12023,7 +12023,7 @@
         <v>2</v>
       </c>
       <c r="E552" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -12044,7 +12044,7 @@
         <v>2</v>
       </c>
       <c r="E553" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -12065,7 +12065,7 @@
         <v>3</v>
       </c>
       <c r="E554" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -12086,7 +12086,7 @@
         <v>2</v>
       </c>
       <c r="E555" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -12107,7 +12107,7 @@
         <v>2</v>
       </c>
       <c r="E556" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -12128,7 +12128,7 @@
         <v>3</v>
       </c>
       <c r="E557" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -12149,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="E558" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
@@ -12170,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="E559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560">
@@ -12191,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="E560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="561">
@@ -12233,7 +12233,7 @@
         <v>2</v>
       </c>
       <c r="E562" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="563">
@@ -12254,7 +12254,7 @@
         <v>2</v>
       </c>
       <c r="E563" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
@@ -12275,7 +12275,7 @@
         <v>1</v>
       </c>
       <c r="E564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
@@ -12296,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="E565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566">
@@ -12401,7 +12401,7 @@
         <v>3</v>
       </c>
       <c r="E570" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -12422,7 +12422,7 @@
         <v>3</v>
       </c>
       <c r="E571" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572">
@@ -12443,7 +12443,7 @@
         <v>2</v>
       </c>
       <c r="E572" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -12464,7 +12464,7 @@
         <v>2</v>
       </c>
       <c r="E573" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -12485,7 +12485,7 @@
         <v>2</v>
       </c>
       <c r="E574" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575">
@@ -12506,7 +12506,7 @@
         <v>2</v>
       </c>
       <c r="E575" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -12527,7 +12527,7 @@
         <v>2</v>
       </c>
       <c r="E576" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -12548,7 +12548,7 @@
         <v>2</v>
       </c>
       <c r="E577" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -12569,7 +12569,7 @@
         <v>2</v>
       </c>
       <c r="E578" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -12590,7 +12590,7 @@
         <v>2</v>
       </c>
       <c r="E579" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580">
@@ -12611,7 +12611,7 @@
         <v>2</v>
       </c>
       <c r="E580" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581">
@@ -12632,7 +12632,7 @@
         <v>2</v>
       </c>
       <c r="E581" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="582">
@@ -12653,7 +12653,7 @@
         <v>2</v>
       </c>
       <c r="E582" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583">
@@ -12674,7 +12674,7 @@
         <v>2</v>
       </c>
       <c r="E583" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="584">
@@ -12695,7 +12695,7 @@
         <v>3</v>
       </c>
       <c r="E584" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -12716,7 +12716,7 @@
         <v>2</v>
       </c>
       <c r="E585" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="586">
@@ -12737,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="E586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="587">
@@ -12758,7 +12758,7 @@
         <v>2</v>
       </c>
       <c r="E587" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
@@ -12779,7 +12779,7 @@
         <v>1</v>
       </c>
       <c r="E588" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="589">
@@ -12800,7 +12800,7 @@
         <v>1</v>
       </c>
       <c r="E589" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590">
@@ -12821,7 +12821,7 @@
         <v>1</v>
       </c>
       <c r="E590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591">
@@ -12842,7 +12842,7 @@
         <v>1</v>
       </c>
       <c r="E591" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="592">
@@ -12863,7 +12863,7 @@
         <v>1</v>
       </c>
       <c r="E592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="593">
@@ -12884,7 +12884,7 @@
         <v>1</v>
       </c>
       <c r="E593" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="594">
@@ -12905,7 +12905,7 @@
         <v>1</v>
       </c>
       <c r="E594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595">
@@ -12926,7 +12926,7 @@
         <v>1</v>
       </c>
       <c r="E595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="596">
@@ -12947,7 +12947,7 @@
         <v>2</v>
       </c>
       <c r="E596" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -12968,7 +12968,7 @@
         <v>2</v>
       </c>
       <c r="E597" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -12989,7 +12989,7 @@
         <v>1</v>
       </c>
       <c r="E598" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="599">
@@ -13010,7 +13010,7 @@
         <v>1</v>
       </c>
       <c r="E599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="600">
@@ -13031,7 +13031,7 @@
         <v>2</v>
       </c>
       <c r="E600" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -13052,7 +13052,7 @@
         <v>2</v>
       </c>
       <c r="E601" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -13073,7 +13073,7 @@
         <v>1</v>
       </c>
       <c r="E602" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603">
@@ -13094,7 +13094,7 @@
         <v>1</v>
       </c>
       <c r="E603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -13115,7 +13115,7 @@
         <v>1</v>
       </c>
       <c r="E604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605">
@@ -13136,7 +13136,7 @@
         <v>2</v>
       </c>
       <c r="E605" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -13157,7 +13157,7 @@
         <v>2</v>
       </c>
       <c r="E606" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -13178,7 +13178,7 @@
         <v>2</v>
       </c>
       <c r="E607" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="608">
@@ -13199,7 +13199,7 @@
         <v>1</v>
       </c>
       <c r="E608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="609">
@@ -13220,7 +13220,7 @@
         <v>1</v>
       </c>
       <c r="E609" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="610">
@@ -13241,7 +13241,7 @@
         <v>1</v>
       </c>
       <c r="E610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="611">
@@ -13262,7 +13262,7 @@
         <v>1</v>
       </c>
       <c r="E611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612">
@@ -13283,7 +13283,7 @@
         <v>3</v>
       </c>
       <c r="E612" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -13304,7 +13304,7 @@
         <v>1</v>
       </c>
       <c r="E613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="614">
@@ -13325,7 +13325,7 @@
         <v>1</v>
       </c>
       <c r="E614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="615">
@@ -13346,7 +13346,7 @@
         <v>2</v>
       </c>
       <c r="E615" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="616">
@@ -13367,7 +13367,7 @@
         <v>2</v>
       </c>
       <c r="E616" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -13388,7 +13388,7 @@
         <v>3</v>
       </c>
       <c r="E617" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -13409,7 +13409,7 @@
         <v>3</v>
       </c>
       <c r="E618" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="619">
@@ -13430,7 +13430,7 @@
         <v>3</v>
       </c>
       <c r="E619" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="620">
@@ -13451,7 +13451,7 @@
         <v>3</v>
       </c>
       <c r="E620" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="621">
@@ -13472,7 +13472,7 @@
         <v>2</v>
       </c>
       <c r="E621" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="622">
@@ -13493,7 +13493,7 @@
         <v>2</v>
       </c>
       <c r="E622" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="623">
@@ -13514,7 +13514,7 @@
         <v>1</v>
       </c>
       <c r="E623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624">
@@ -13535,7 +13535,7 @@
         <v>2</v>
       </c>
       <c r="E624" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="625">
@@ -13556,7 +13556,7 @@
         <v>2</v>
       </c>
       <c r="E625" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626">
@@ -13577,7 +13577,7 @@
         <v>2</v>
       </c>
       <c r="E626" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
@@ -13598,7 +13598,7 @@
         <v>2</v>
       </c>
       <c r="E627" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -13619,7 +13619,7 @@
         <v>2</v>
       </c>
       <c r="E628" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="629">
@@ -13640,7 +13640,7 @@
         <v>2</v>
       </c>
       <c r="E629" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="630">
@@ -13661,7 +13661,7 @@
         <v>2</v>
       </c>
       <c r="E630" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="631">
@@ -13682,7 +13682,7 @@
         <v>1</v>
       </c>
       <c r="E631" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="632">
@@ -13724,7 +13724,7 @@
         <v>1</v>
       </c>
       <c r="E633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="634">
@@ -13745,7 +13745,7 @@
         <v>1</v>
       </c>
       <c r="E634" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="635">
@@ -13766,7 +13766,7 @@
         <v>1</v>
       </c>
       <c r="E635" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="636">
@@ -13787,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="E636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
@@ -13808,7 +13808,7 @@
         <v>1</v>
       </c>
       <c r="E637" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="638">
@@ -13850,7 +13850,7 @@
         <v>2</v>
       </c>
       <c r="E639" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -13871,7 +13871,7 @@
         <v>2</v>
       </c>
       <c r="E640" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -13892,7 +13892,7 @@
         <v>2</v>
       </c>
       <c r="E641" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -13913,7 +13913,7 @@
         <v>2</v>
       </c>
       <c r="E642" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
@@ -13934,7 +13934,7 @@
         <v>2</v>
       </c>
       <c r="E643" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -13955,7 +13955,7 @@
         <v>1</v>
       </c>
       <c r="E644" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
@@ -13976,7 +13976,7 @@
         <v>1</v>
       </c>
       <c r="E645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="646">
@@ -13997,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="E646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="647">
@@ -14312,7 +14312,7 @@
         <v>1</v>
       </c>
       <c r="E661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="662">
@@ -14333,7 +14333,7 @@
         <v>1</v>
       </c>
       <c r="E662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="663">
@@ -14354,7 +14354,7 @@
         <v>1</v>
       </c>
       <c r="E663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="664">
@@ -14375,7 +14375,7 @@
         <v>1</v>
       </c>
       <c r="E664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665">
@@ -14396,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="E665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666">
@@ -14417,7 +14417,7 @@
         <v>1</v>
       </c>
       <c r="E666" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="667">
@@ -14438,7 +14438,7 @@
         <v>1</v>
       </c>
       <c r="E667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="E668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
@@ -14480,7 +14480,7 @@
         <v>1</v>
       </c>
       <c r="E669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
@@ -14858,7 +14858,7 @@
         <v>1</v>
       </c>
       <c r="E687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688">
@@ -14879,7 +14879,7 @@
         <v>1</v>
       </c>
       <c r="E688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="689">
@@ -14900,7 +14900,7 @@
         <v>1</v>
       </c>
       <c r="E689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="690">
@@ -14921,7 +14921,7 @@
         <v>2</v>
       </c>
       <c r="E690" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="691">
@@ -14942,7 +14942,7 @@
         <v>2</v>
       </c>
       <c r="E691" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="692">
@@ -14963,7 +14963,7 @@
         <v>2</v>
       </c>
       <c r="E692" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="693">
@@ -14984,7 +14984,7 @@
         <v>2</v>
       </c>
       <c r="E693" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="694">
@@ -15005,7 +15005,7 @@
         <v>1</v>
       </c>
       <c r="E694" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695">
@@ -15026,7 +15026,7 @@
         <v>1</v>
       </c>
       <c r="E695" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="696">
@@ -15047,7 +15047,7 @@
         <v>3</v>
       </c>
       <c r="E696" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="697">
@@ -15068,7 +15068,7 @@
         <v>1</v>
       </c>
       <c r="E697" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="698">
@@ -15089,7 +15089,7 @@
         <v>1</v>
       </c>
       <c r="E698" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699">
@@ -15110,7 +15110,7 @@
         <v>1</v>
       </c>
       <c r="E699" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="700">
@@ -15131,7 +15131,7 @@
         <v>1</v>
       </c>
       <c r="E700" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="701">
@@ -15152,7 +15152,7 @@
         <v>1</v>
       </c>
       <c r="E701" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702">
@@ -15362,7 +15362,7 @@
         <v>3</v>
       </c>
       <c r="E711" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="712">
@@ -15383,7 +15383,7 @@
         <v>4</v>
       </c>
       <c r="E712" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
